--- a/docs/validacao-visual/2026-10-vendas-mapa/vendas-27-meses.xlsx
+++ b/docs/validacao-visual/2026-10-vendas-mapa/vendas-27-meses.xlsx
@@ -410,7 +410,7 @@
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
@@ -438,9 +438,9 @@
     <col min="31" max="31" width="14.83203125" customWidth="1"/>
     <col min="32" max="32" width="14.83203125" customWidth="1"/>
     <col min="33" max="33" width="14.83203125" customWidth="1"/>
-    <col min="34" max="34" width="14.83203125" customWidth="1"/>
-    <col min="35" max="35" width="14.83203125" customWidth="1"/>
-    <col min="36" max="36" width="22.83203125" customWidth="1"/>
+    <col min="34" max="34" width="22.83203125" customWidth="1"/>
+    <col min="35" max="35" width="27.83203125" customWidth="1"/>
+    <col min="36" max="36" width="31.83203125" customWidth="1"/>
     <col min="37" max="37" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -456,7 +456,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gerado em: 16/10/2026, 10:48</v>
+        <v>Gerado em: 16/10/2026, 11:17</v>
       </c>
     </row>
     <row r="5">
@@ -591,127 +591,127 @@
 unit. est.</v>
       </c>
       <c r="F22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Custo total
-est.</v>
-      </c>
-      <c r="G22" t="str" xml:space="preserve">
         <v xml:space="preserve">Jul
 24</v>
       </c>
-      <c r="H22" t="str" xml:space="preserve">
+      <c r="G22" t="str" xml:space="preserve">
         <v xml:space="preserve">Ago
 24</v>
       </c>
-      <c r="I22" t="str" xml:space="preserve">
+      <c r="H22" t="str" xml:space="preserve">
         <v xml:space="preserve">Set
 24</v>
       </c>
-      <c r="J22" t="str" xml:space="preserve">
+      <c r="I22" t="str" xml:space="preserve">
         <v xml:space="preserve">Out
 24</v>
       </c>
-      <c r="K22" t="str" xml:space="preserve">
+      <c r="J22" t="str" xml:space="preserve">
         <v xml:space="preserve">Nov
 24</v>
       </c>
-      <c r="L22" t="str" xml:space="preserve">
+      <c r="K22" t="str" xml:space="preserve">
         <v xml:space="preserve">Dez
 24</v>
       </c>
-      <c r="M22" t="str" xml:space="preserve">
+      <c r="L22" t="str" xml:space="preserve">
         <v xml:space="preserve">Jan
 25</v>
       </c>
-      <c r="N22" t="str" xml:space="preserve">
+      <c r="M22" t="str" xml:space="preserve">
         <v xml:space="preserve">Fev
 25</v>
       </c>
-      <c r="O22" t="str" xml:space="preserve">
+      <c r="N22" t="str" xml:space="preserve">
         <v xml:space="preserve">Mar
 25</v>
       </c>
-      <c r="P22" t="str" xml:space="preserve">
+      <c r="O22" t="str" xml:space="preserve">
         <v xml:space="preserve">Abr
 25</v>
       </c>
-      <c r="Q22" t="str" xml:space="preserve">
+      <c r="P22" t="str" xml:space="preserve">
         <v xml:space="preserve">Mai
 25</v>
       </c>
-      <c r="R22" t="str" xml:space="preserve">
+      <c r="Q22" t="str" xml:space="preserve">
         <v xml:space="preserve">Jun
 25</v>
       </c>
-      <c r="S22" t="str" xml:space="preserve">
+      <c r="R22" t="str" xml:space="preserve">
         <v xml:space="preserve">Jul
 25</v>
       </c>
-      <c r="T22" t="str" xml:space="preserve">
+      <c r="S22" t="str" xml:space="preserve">
         <v xml:space="preserve">Ago
 25</v>
       </c>
-      <c r="U22" t="str" xml:space="preserve">
+      <c r="T22" t="str" xml:space="preserve">
         <v xml:space="preserve">Set
 25</v>
       </c>
-      <c r="V22" t="str" xml:space="preserve">
+      <c r="U22" t="str" xml:space="preserve">
         <v xml:space="preserve">Out
 25</v>
       </c>
-      <c r="W22" t="str" xml:space="preserve">
+      <c r="V22" t="str" xml:space="preserve">
         <v xml:space="preserve">Nov
 25</v>
       </c>
-      <c r="X22" t="str" xml:space="preserve">
+      <c r="W22" t="str" xml:space="preserve">
         <v xml:space="preserve">Dez
 25</v>
       </c>
-      <c r="Y22" t="str" xml:space="preserve">
+      <c r="X22" t="str" xml:space="preserve">
         <v xml:space="preserve">Jan
 26</v>
       </c>
-      <c r="Z22" t="str" xml:space="preserve">
+      <c r="Y22" t="str" xml:space="preserve">
         <v xml:space="preserve">Fev
 26</v>
       </c>
-      <c r="AA22" t="str" xml:space="preserve">
+      <c r="Z22" t="str" xml:space="preserve">
         <v xml:space="preserve">Mar
 26</v>
       </c>
-      <c r="AB22" t="str" xml:space="preserve">
+      <c r="AA22" t="str" xml:space="preserve">
         <v xml:space="preserve">Abr
 26</v>
       </c>
-      <c r="AC22" t="str" xml:space="preserve">
+      <c r="AB22" t="str" xml:space="preserve">
         <v xml:space="preserve">Mai
 26</v>
       </c>
-      <c r="AD22" t="str" xml:space="preserve">
+      <c r="AC22" t="str" xml:space="preserve">
         <v xml:space="preserve">Jun
 26</v>
       </c>
-      <c r="AE22" t="str" xml:space="preserve">
+      <c r="AD22" t="str" xml:space="preserve">
         <v xml:space="preserve">Jul
 26</v>
       </c>
-      <c r="AF22" t="str" xml:space="preserve">
+      <c r="AE22" t="str" xml:space="preserve">
         <v xml:space="preserve">Ago
 26</v>
       </c>
-      <c r="AG22" t="str" xml:space="preserve">
+      <c r="AF22" t="str" xml:space="preserve">
         <v xml:space="preserve">Set
 26</v>
       </c>
+      <c r="AG22" t="str">
+        <v>Stock</v>
+      </c>
       <c r="AH22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Total
-Unid.</v>
-      </c>
-      <c r="AI22" t="str">
-        <v>Stock</v>
+        <v xml:space="preserve">Período:
+Total unid.</v>
+      </c>
+      <c r="AI22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Período: custo
+total est.</v>
       </c>
       <c r="AJ22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Valor Vendas
-(s/IVA)</v>
+        <v xml:space="preserve">Período: valor
+vendas (s/IVA)</v>
       </c>
       <c r="AK22" t="str">
         <v>Tipo de linha</v>
@@ -733,8 +733,8 @@
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="1">
-        <v>4</v>
+      <c r="F23" s="2">
+        <v>0</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
@@ -812,16 +812,16 @@
         <v>0</v>
       </c>
       <c r="AF23" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG23" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AH23" s="2">
         <v>2</v>
       </c>
-      <c r="AI23" s="2">
-        <v>7</v>
+      <c r="AI23" s="1">
+        <v>4</v>
       </c>
       <c r="AJ23" s="1">
         <v>40</v>
@@ -846,8 +846,8 @@
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="1">
-        <v>4</v>
+      <c r="F24" s="2">
+        <v>0</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
@@ -925,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="AF24" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG24" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AH24" s="2">
         <v>2</v>
       </c>
-      <c r="AI24" s="2">
-        <v>7</v>
+      <c r="AI24" s="1">
+        <v>4</v>
       </c>
       <c r="AJ24" s="1">
         <v>40</v>
@@ -959,8 +959,8 @@
       <c r="E25" s="1">
         <v>4</v>
       </c>
-      <c r="F25" s="1">
-        <v>216</v>
+      <c r="F25" s="2">
+        <v>2</v>
       </c>
       <c r="G25" s="2">
         <v>2</v>
@@ -1041,13 +1041,13 @@
         <v>2</v>
       </c>
       <c r="AG25" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH25" s="2">
         <v>54</v>
       </c>
-      <c r="AI25" s="2">
-        <v>6</v>
+      <c r="AI25" s="1">
+        <v>216</v>
       </c>
       <c r="AJ25" s="1">
         <v>1080</v>
@@ -1072,8 +1072,8 @@
       <c r="E26" s="1">
         <v>5</v>
       </c>
-      <c r="F26" s="1">
-        <v>405</v>
+      <c r="F26" s="2">
+        <v>3</v>
       </c>
       <c r="G26" s="2">
         <v>3</v>
@@ -1154,13 +1154,13 @@
         <v>3</v>
       </c>
       <c r="AG26" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH26" s="2">
         <v>81</v>
       </c>
-      <c r="AI26" s="2">
-        <v>6</v>
+      <c r="AI26" s="1">
+        <v>405</v>
       </c>
       <c r="AJ26" s="1">
         <v>1620</v>
@@ -1185,8 +1185,8 @@
       <c r="E27" s="1">
         <v>6</v>
       </c>
-      <c r="F27" s="1">
-        <v>486</v>
+      <c r="F27" s="2">
+        <v>3</v>
       </c>
       <c r="G27" s="2">
         <v>3</v>
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="AG27" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH27" s="2">
         <v>81</v>
       </c>
-      <c r="AI27" s="2">
-        <v>5</v>
+      <c r="AI27" s="1">
+        <v>486</v>
       </c>
       <c r="AJ27" s="1">
         <v>1620</v>
@@ -1298,8 +1298,8 @@
       <c r="E28" t="str">
         <v/>
       </c>
-      <c r="F28" s="1">
-        <v>891</v>
+      <c r="F28" s="2">
+        <v>6</v>
       </c>
       <c r="G28" s="2">
         <v>6</v>
@@ -1380,13 +1380,13 @@
         <v>6</v>
       </c>
       <c r="AG28" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AH28" s="2">
         <v>162</v>
       </c>
-      <c r="AI28" s="2">
-        <v>11</v>
+      <c r="AI28" s="1">
+        <v>891</v>
       </c>
       <c r="AJ28" s="1">
         <v>3240</v>
@@ -1411,8 +1411,8 @@
       <c r="E29" s="1">
         <v>6</v>
       </c>
-      <c r="F29" s="1">
-        <v>162</v>
+      <c r="F29" s="2">
+        <v>1</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -1493,13 +1493,13 @@
         <v>1</v>
       </c>
       <c r="AG29" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH29" s="2">
         <v>27</v>
       </c>
-      <c r="AI29" s="2">
-        <v>6</v>
+      <c r="AI29" s="1">
+        <v>162</v>
       </c>
       <c r="AJ29" s="1">
         <v>540</v>
@@ -1524,8 +1524,8 @@
       <c r="E30" s="1">
         <v>7</v>
       </c>
-      <c r="F30" s="1">
-        <v>378</v>
+      <c r="F30" s="2">
+        <v>2</v>
       </c>
       <c r="G30" s="2">
         <v>2</v>
@@ -1606,13 +1606,13 @@
         <v>2</v>
       </c>
       <c r="AG30" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH30" s="2">
         <v>54</v>
       </c>
-      <c r="AI30" s="2">
-        <v>6</v>
+      <c r="AI30" s="1">
+        <v>378</v>
       </c>
       <c r="AJ30" s="1">
         <v>1080</v>
@@ -1637,8 +1637,8 @@
       <c r="E31" s="1">
         <v>8</v>
       </c>
-      <c r="F31" s="1">
-        <v>216</v>
+      <c r="F31" s="2">
+        <v>1</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -1719,13 +1719,13 @@
         <v>1</v>
       </c>
       <c r="AG31" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH31" s="2">
         <v>27</v>
       </c>
-      <c r="AI31" s="2">
-        <v>5</v>
+      <c r="AI31" s="1">
+        <v>216</v>
       </c>
       <c r="AJ31" s="1">
         <v>540</v>
@@ -1750,8 +1750,8 @@
       <c r="E32" t="str">
         <v/>
       </c>
-      <c r="F32" s="1">
-        <v>594</v>
+      <c r="F32" s="2">
+        <v>3</v>
       </c>
       <c r="G32" s="2">
         <v>3</v>
@@ -1832,13 +1832,13 @@
         <v>3</v>
       </c>
       <c r="AG32" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AH32" s="2">
         <v>81</v>
       </c>
-      <c r="AI32" s="2">
-        <v>11</v>
+      <c r="AI32" s="1">
+        <v>594</v>
       </c>
       <c r="AJ32" s="1">
         <v>1620</v>
@@ -1863,8 +1863,8 @@
       <c r="E33" s="1">
         <v>3</v>
       </c>
-      <c r="F33" s="1">
-        <v>243</v>
+      <c r="F33" s="2">
+        <v>3</v>
       </c>
       <c r="G33" s="2">
         <v>3</v>
@@ -1945,13 +1945,13 @@
         <v>3</v>
       </c>
       <c r="AG33" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH33" s="2">
         <v>81</v>
       </c>
-      <c r="AI33" s="2">
-        <v>6</v>
+      <c r="AI33" s="1">
+        <v>243</v>
       </c>
       <c r="AJ33" s="1">
         <v>1620</v>
@@ -1976,8 +1976,8 @@
       <c r="E34" s="1">
         <v>4</v>
       </c>
-      <c r="F34" s="1">
-        <v>108</v>
+      <c r="F34" s="2">
+        <v>1</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -2058,13 +2058,13 @@
         <v>1</v>
       </c>
       <c r="AG34" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH34" s="2">
         <v>27</v>
       </c>
-      <c r="AI34" s="2">
-        <v>6</v>
+      <c r="AI34" s="1">
+        <v>108</v>
       </c>
       <c r="AJ34" s="1">
         <v>540</v>
@@ -2089,8 +2089,8 @@
       <c r="E35" s="1">
         <v>5</v>
       </c>
-      <c r="F35" s="1">
-        <v>405</v>
+      <c r="F35" s="2">
+        <v>3</v>
       </c>
       <c r="G35" s="2">
         <v>3</v>
@@ -2171,13 +2171,13 @@
         <v>3</v>
       </c>
       <c r="AG35" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH35" s="2">
         <v>81</v>
       </c>
-      <c r="AI35" s="2">
-        <v>5</v>
+      <c r="AI35" s="1">
+        <v>405</v>
       </c>
       <c r="AJ35" s="1">
         <v>1620</v>
@@ -2202,8 +2202,8 @@
       <c r="E36" t="str">
         <v/>
       </c>
-      <c r="F36" s="1">
-        <v>513</v>
+      <c r="F36" s="2">
+        <v>4</v>
       </c>
       <c r="G36" s="2">
         <v>4</v>
@@ -2284,13 +2284,13 @@
         <v>4</v>
       </c>
       <c r="AG36" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH36" s="2">
         <v>108</v>
       </c>
-      <c r="AI36" s="2">
-        <v>11</v>
+      <c r="AI36" s="1">
+        <v>513</v>
       </c>
       <c r="AJ36" s="1">
         <v>2160</v>
@@ -2315,8 +2315,8 @@
       <c r="E37" s="1">
         <v>5</v>
       </c>
-      <c r="F37" s="1">
-        <v>270</v>
+      <c r="F37" s="2">
+        <v>2</v>
       </c>
       <c r="G37" s="2">
         <v>2</v>
@@ -2397,13 +2397,13 @@
         <v>2</v>
       </c>
       <c r="AG37" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH37" s="2">
         <v>54</v>
       </c>
-      <c r="AI37" s="2">
-        <v>6</v>
+      <c r="AI37" s="1">
+        <v>270</v>
       </c>
       <c r="AJ37" s="1">
         <v>1080</v>
@@ -2428,8 +2428,8 @@
       <c r="E38" s="1">
         <v>6</v>
       </c>
-      <c r="F38" s="1">
-        <v>486</v>
+      <c r="F38" s="2">
+        <v>3</v>
       </c>
       <c r="G38" s="2">
         <v>3</v>
@@ -2510,13 +2510,13 @@
         <v>3</v>
       </c>
       <c r="AG38" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH38" s="2">
         <v>81</v>
       </c>
-      <c r="AI38" s="2">
-        <v>6</v>
+      <c r="AI38" s="1">
+        <v>486</v>
       </c>
       <c r="AJ38" s="1">
         <v>1620</v>
@@ -2541,8 +2541,8 @@
       <c r="E39" s="1">
         <v>7</v>
       </c>
-      <c r="F39" s="1">
-        <v>189</v>
+      <c r="F39" s="2">
+        <v>1</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -2623,13 +2623,13 @@
         <v>1</v>
       </c>
       <c r="AG39" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH39" s="2">
         <v>27</v>
       </c>
-      <c r="AI39" s="2">
-        <v>5</v>
+      <c r="AI39" s="1">
+        <v>189</v>
       </c>
       <c r="AJ39" s="1">
         <v>540</v>
@@ -2654,8 +2654,8 @@
       <c r="E40" t="str">
         <v/>
       </c>
-      <c r="F40" s="1">
-        <v>675</v>
+      <c r="F40" s="2">
+        <v>4</v>
       </c>
       <c r="G40" s="2">
         <v>4</v>
@@ -2736,13 +2736,13 @@
         <v>4</v>
       </c>
       <c r="AG40" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH40" s="2">
         <v>108</v>
       </c>
-      <c r="AI40" s="2">
-        <v>11</v>
+      <c r="AI40" s="1">
+        <v>675</v>
       </c>
       <c r="AJ40" s="1">
         <v>2160</v>
@@ -2767,8 +2767,8 @@
       <c r="E41" s="1">
         <v>7</v>
       </c>
-      <c r="F41" s="1">
-        <v>189</v>
+      <c r="F41" s="2">
+        <v>1</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -2849,13 +2849,13 @@
         <v>1</v>
       </c>
       <c r="AG41" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH41" s="2">
         <v>27</v>
       </c>
-      <c r="AI41" s="2">
-        <v>6</v>
+      <c r="AI41" s="1">
+        <v>189</v>
       </c>
       <c r="AJ41" s="1">
         <v>540</v>
@@ -2880,8 +2880,8 @@
       <c r="E42" s="1">
         <v>3</v>
       </c>
-      <c r="F42" s="1">
-        <v>162</v>
+      <c r="F42" s="2">
+        <v>2</v>
       </c>
       <c r="G42" s="2">
         <v>2</v>
@@ -2962,13 +2962,13 @@
         <v>2</v>
       </c>
       <c r="AG42" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH42" s="2">
         <v>54</v>
       </c>
-      <c r="AI42" s="2">
-        <v>6</v>
+      <c r="AI42" s="1">
+        <v>162</v>
       </c>
       <c r="AJ42" s="1">
         <v>1080</v>
@@ -2993,8 +2993,8 @@
       <c r="E43" s="1">
         <v>4</v>
       </c>
-      <c r="F43" s="1">
-        <v>324</v>
+      <c r="F43" s="2">
+        <v>3</v>
       </c>
       <c r="G43" s="2">
         <v>3</v>
@@ -3075,13 +3075,13 @@
         <v>3</v>
       </c>
       <c r="AG43" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH43" s="2">
         <v>81</v>
       </c>
-      <c r="AI43" s="2">
-        <v>5</v>
+      <c r="AI43" s="1">
+        <v>324</v>
       </c>
       <c r="AJ43" s="1">
         <v>1620</v>
@@ -3106,8 +3106,8 @@
       <c r="E44" t="str">
         <v/>
       </c>
-      <c r="F44" s="1">
-        <v>486</v>
+      <c r="F44" s="2">
+        <v>5</v>
       </c>
       <c r="G44" s="2">
         <v>5</v>
@@ -3188,13 +3188,13 @@
         <v>5</v>
       </c>
       <c r="AG44" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AH44" s="2">
         <v>135</v>
       </c>
-      <c r="AI44" s="2">
-        <v>11</v>
+      <c r="AI44" s="1">
+        <v>486</v>
       </c>
       <c r="AJ44" s="1">
         <v>2700</v>
@@ -3219,8 +3219,8 @@
       <c r="E45" s="1">
         <v>4</v>
       </c>
-      <c r="F45" s="1">
-        <v>324</v>
+      <c r="F45" s="2">
+        <v>3</v>
       </c>
       <c r="G45" s="2">
         <v>3</v>
@@ -3301,13 +3301,13 @@
         <v>3</v>
       </c>
       <c r="AG45" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH45" s="2">
         <v>81</v>
       </c>
-      <c r="AI45" s="2">
-        <v>6</v>
+      <c r="AI45" s="1">
+        <v>324</v>
       </c>
       <c r="AJ45" s="1">
         <v>1620</v>
@@ -3332,8 +3332,8 @@
       <c r="E46" s="1">
         <v>5</v>
       </c>
-      <c r="F46" s="1">
-        <v>135</v>
+      <c r="F46" s="2">
+        <v>1</v>
       </c>
       <c r="G46" s="2">
         <v>1</v>
@@ -3414,13 +3414,13 @@
         <v>1</v>
       </c>
       <c r="AG46" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH46" s="2">
         <v>27</v>
       </c>
-      <c r="AI46" s="2">
-        <v>6</v>
+      <c r="AI46" s="1">
+        <v>135</v>
       </c>
       <c r="AJ46" s="1">
         <v>540</v>
@@ -3445,8 +3445,8 @@
       <c r="E47" s="1">
         <v>6</v>
       </c>
-      <c r="F47" s="1">
-        <v>162</v>
+      <c r="F47" s="2">
+        <v>1</v>
       </c>
       <c r="G47" s="2">
         <v>1</v>
@@ -3527,13 +3527,13 @@
         <v>1</v>
       </c>
       <c r="AG47" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH47" s="2">
         <v>27</v>
       </c>
-      <c r="AI47" s="2">
-        <v>5</v>
+      <c r="AI47" s="1">
+        <v>162</v>
       </c>
       <c r="AJ47" s="1">
         <v>540</v>
@@ -3558,8 +3558,8 @@
       <c r="E48" t="str">
         <v/>
       </c>
-      <c r="F48" s="1">
-        <v>297</v>
+      <c r="F48" s="2">
+        <v>2</v>
       </c>
       <c r="G48" s="2">
         <v>2</v>
@@ -3640,13 +3640,13 @@
         <v>2</v>
       </c>
       <c r="AG48" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AH48" s="2">
         <v>54</v>
       </c>
-      <c r="AI48" s="2">
-        <v>11</v>
+      <c r="AI48" s="1">
+        <v>297</v>
       </c>
       <c r="AJ48" s="1">
         <v>1080</v>
@@ -3671,8 +3671,8 @@
       <c r="E49" s="1">
         <v>6</v>
       </c>
-      <c r="F49" s="1">
-        <v>324</v>
+      <c r="F49" s="2">
+        <v>2</v>
       </c>
       <c r="G49" s="2">
         <v>2</v>
@@ -3753,13 +3753,13 @@
         <v>2</v>
       </c>
       <c r="AG49" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH49" s="2">
         <v>54</v>
       </c>
-      <c r="AI49" s="2">
-        <v>6</v>
+      <c r="AI49" s="1">
+        <v>324</v>
       </c>
       <c r="AJ49" s="1">
         <v>1080</v>
@@ -3784,8 +3784,8 @@
       <c r="E50" s="1">
         <v>7</v>
       </c>
-      <c r="F50" s="1">
-        <v>567</v>
+      <c r="F50" s="2">
+        <v>3</v>
       </c>
       <c r="G50" s="2">
         <v>3</v>
@@ -3866,13 +3866,13 @@
         <v>3</v>
       </c>
       <c r="AG50" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH50" s="2">
         <v>81</v>
       </c>
-      <c r="AI50" s="2">
-        <v>6</v>
+      <c r="AI50" s="1">
+        <v>567</v>
       </c>
       <c r="AJ50" s="1">
         <v>1620</v>
@@ -3897,8 +3897,8 @@
       <c r="E51" s="1">
         <v>8</v>
       </c>
-      <c r="F51" s="1">
-        <v>648</v>
+      <c r="F51" s="2">
+        <v>3</v>
       </c>
       <c r="G51" s="2">
         <v>3</v>
@@ -3979,13 +3979,13 @@
         <v>3</v>
       </c>
       <c r="AG51" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH51" s="2">
         <v>81</v>
       </c>
-      <c r="AI51" s="2">
-        <v>5</v>
+      <c r="AI51" s="1">
+        <v>648</v>
       </c>
       <c r="AJ51" s="1">
         <v>1620</v>
@@ -4010,8 +4010,8 @@
       <c r="E52" t="str">
         <v/>
       </c>
-      <c r="F52" s="1">
-        <v>1215</v>
+      <c r="F52" s="2">
+        <v>6</v>
       </c>
       <c r="G52" s="2">
         <v>6</v>
@@ -4092,13 +4092,13 @@
         <v>6</v>
       </c>
       <c r="AG52" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AH52" s="2">
         <v>162</v>
       </c>
-      <c r="AI52" s="2">
-        <v>11</v>
+      <c r="AI52" s="1">
+        <v>1215</v>
       </c>
       <c r="AJ52" s="1">
         <v>3240</v>
@@ -4123,8 +4123,8 @@
       <c r="E53" s="1">
         <v>3</v>
       </c>
-      <c r="F53" s="1">
-        <v>81</v>
+      <c r="F53" s="2">
+        <v>1</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
@@ -4205,13 +4205,13 @@
         <v>1</v>
       </c>
       <c r="AG53" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH53" s="2">
         <v>27</v>
       </c>
-      <c r="AI53" s="2">
-        <v>6</v>
+      <c r="AI53" s="1">
+        <v>81</v>
       </c>
       <c r="AJ53" s="1">
         <v>540</v>
@@ -4236,8 +4236,8 @@
       <c r="E54" s="1">
         <v>4</v>
       </c>
-      <c r="F54" s="1">
-        <v>216</v>
+      <c r="F54" s="2">
+        <v>2</v>
       </c>
       <c r="G54" s="2">
         <v>2</v>
@@ -4318,13 +4318,13 @@
         <v>2</v>
       </c>
       <c r="AG54" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH54" s="2">
         <v>54</v>
       </c>
-      <c r="AI54" s="2">
-        <v>6</v>
+      <c r="AI54" s="1">
+        <v>216</v>
       </c>
       <c r="AJ54" s="1">
         <v>1080</v>
@@ -4349,8 +4349,8 @@
       <c r="E55" s="1">
         <v>5</v>
       </c>
-      <c r="F55" s="1">
-        <v>135</v>
+      <c r="F55" s="2">
+        <v>1</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -4431,13 +4431,13 @@
         <v>1</v>
       </c>
       <c r="AG55" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH55" s="2">
         <v>27</v>
       </c>
-      <c r="AI55" s="2">
-        <v>5</v>
+      <c r="AI55" s="1">
+        <v>135</v>
       </c>
       <c r="AJ55" s="1">
         <v>540</v>
@@ -4462,8 +4462,8 @@
       <c r="E56" t="str">
         <v/>
       </c>
-      <c r="F56" s="1">
-        <v>351</v>
+      <c r="F56" s="2">
+        <v>3</v>
       </c>
       <c r="G56" s="2">
         <v>3</v>
@@ -4544,13 +4544,13 @@
         <v>3</v>
       </c>
       <c r="AG56" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AH56" s="2">
         <v>81</v>
       </c>
-      <c r="AI56" s="2">
-        <v>11</v>
+      <c r="AI56" s="1">
+        <v>351</v>
       </c>
       <c r="AJ56" s="1">
         <v>1620</v>
@@ -4575,8 +4575,8 @@
       <c r="E57" s="1">
         <v>5</v>
       </c>
-      <c r="F57" s="1">
-        <v>405</v>
+      <c r="F57" s="2">
+        <v>3</v>
       </c>
       <c r="G57" s="2">
         <v>3</v>
@@ -4657,13 +4657,13 @@
         <v>3</v>
       </c>
       <c r="AG57" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH57" s="2">
         <v>81</v>
       </c>
-      <c r="AI57" s="2">
-        <v>6</v>
+      <c r="AI57" s="1">
+        <v>405</v>
       </c>
       <c r="AJ57" s="1">
         <v>1620</v>
@@ -4688,8 +4688,8 @@
       <c r="E58" s="1">
         <v>6</v>
       </c>
-      <c r="F58" s="1">
-        <v>162</v>
+      <c r="F58" s="2">
+        <v>1</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
@@ -4770,13 +4770,13 @@
         <v>1</v>
       </c>
       <c r="AG58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH58" s="2">
         <v>27</v>
       </c>
-      <c r="AI58" s="2">
-        <v>0</v>
+      <c r="AI58" s="1">
+        <v>162</v>
       </c>
       <c r="AJ58" s="1">
         <v>540</v>
@@ -4801,8 +4801,8 @@
       <c r="E59" s="1">
         <v>7</v>
       </c>
-      <c r="F59" s="1">
-        <v>567</v>
+      <c r="F59" s="2">
+        <v>3</v>
       </c>
       <c r="G59" s="2">
         <v>3</v>
@@ -4883,13 +4883,13 @@
         <v>3</v>
       </c>
       <c r="AG59" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH59" s="2">
         <v>81</v>
       </c>
-      <c r="AI59" s="2">
-        <v>5</v>
+      <c r="AI59" s="1">
+        <v>567</v>
       </c>
       <c r="AJ59" s="1">
         <v>1620</v>
@@ -4914,8 +4914,8 @@
       <c r="E60" t="str">
         <v/>
       </c>
-      <c r="F60" s="1">
-        <v>729</v>
+      <c r="F60" s="2">
+        <v>4</v>
       </c>
       <c r="G60" s="2">
         <v>4</v>
@@ -4996,13 +4996,13 @@
         <v>4</v>
       </c>
       <c r="AG60" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH60" s="2">
         <v>108</v>
       </c>
-      <c r="AI60" s="2">
-        <v>5</v>
+      <c r="AI60" s="1">
+        <v>729</v>
       </c>
       <c r="AJ60" s="1">
         <v>2160</v>
@@ -5027,8 +5027,8 @@
       <c r="E61" s="1">
         <v>7</v>
       </c>
-      <c r="F61" s="1">
-        <v>378</v>
+      <c r="F61" s="2">
+        <v>2</v>
       </c>
       <c r="G61" s="2">
         <v>2</v>
@@ -5109,13 +5109,13 @@
         <v>2</v>
       </c>
       <c r="AG61" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH61" s="2">
         <v>54</v>
       </c>
-      <c r="AI61" s="2">
-        <v>6</v>
+      <c r="AI61" s="1">
+        <v>378</v>
       </c>
       <c r="AJ61" s="1">
         <v>1080</v>
@@ -5140,8 +5140,8 @@
       <c r="E62" s="1">
         <v>3</v>
       </c>
-      <c r="F62" s="1">
-        <v>243</v>
+      <c r="F62" s="2">
+        <v>3</v>
       </c>
       <c r="G62" s="2">
         <v>3</v>
@@ -5222,13 +5222,13 @@
         <v>3</v>
       </c>
       <c r="AG62" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH62" s="2">
         <v>81</v>
       </c>
-      <c r="AI62" s="2">
-        <v>6</v>
+      <c r="AI62" s="1">
+        <v>243</v>
       </c>
       <c r="AJ62" s="1">
         <v>1620</v>
@@ -5253,8 +5253,8 @@
       <c r="E63" s="1">
         <v>4</v>
       </c>
-      <c r="F63" s="1">
-        <v>108</v>
+      <c r="F63" s="2">
+        <v>1</v>
       </c>
       <c r="G63" s="2">
         <v>1</v>
@@ -5335,13 +5335,13 @@
         <v>1</v>
       </c>
       <c r="AG63" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH63" s="2">
         <v>27</v>
       </c>
-      <c r="AI63" s="2">
-        <v>5</v>
+      <c r="AI63" s="1">
+        <v>108</v>
       </c>
       <c r="AJ63" s="1">
         <v>540</v>
@@ -5366,8 +5366,8 @@
       <c r="E64" t="str">
         <v/>
       </c>
-      <c r="F64" s="1">
-        <v>351</v>
+      <c r="F64" s="2">
+        <v>4</v>
       </c>
       <c r="G64" s="2">
         <v>4</v>
@@ -5448,13 +5448,13 @@
         <v>4</v>
       </c>
       <c r="AG64" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH64" s="2">
         <v>108</v>
       </c>
-      <c r="AI64" s="2">
-        <v>11</v>
+      <c r="AI64" s="1">
+        <v>351</v>
       </c>
       <c r="AJ64" s="1">
         <v>2160</v>
@@ -5479,8 +5479,8 @@
       <c r="E65" s="1">
         <v>4</v>
       </c>
-      <c r="F65" s="1">
-        <v>108</v>
+      <c r="F65" s="2">
+        <v>1</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -5561,13 +5561,13 @@
         <v>1</v>
       </c>
       <c r="AG65" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH65" s="2">
         <v>27</v>
       </c>
-      <c r="AI65" s="2">
-        <v>6</v>
+      <c r="AI65" s="1">
+        <v>108</v>
       </c>
       <c r="AJ65" s="1">
         <v>540</v>
@@ -5592,8 +5592,8 @@
       <c r="E66" s="1">
         <v>5</v>
       </c>
-      <c r="F66" s="1">
-        <v>270</v>
+      <c r="F66" s="2">
+        <v>2</v>
       </c>
       <c r="G66" s="2">
         <v>2</v>
@@ -5674,13 +5674,13 @@
         <v>2</v>
       </c>
       <c r="AG66" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH66" s="2">
         <v>54</v>
       </c>
-      <c r="AI66" s="2">
-        <v>6</v>
+      <c r="AI66" s="1">
+        <v>270</v>
       </c>
       <c r="AJ66" s="1">
         <v>1080</v>
@@ -5705,8 +5705,8 @@
       <c r="E67" s="1">
         <v>6</v>
       </c>
-      <c r="F67" s="1">
-        <v>486</v>
+      <c r="F67" s="2">
+        <v>3</v>
       </c>
       <c r="G67" s="2">
         <v>3</v>
@@ -5787,13 +5787,13 @@
         <v>3</v>
       </c>
       <c r="AG67" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH67" s="2">
         <v>81</v>
       </c>
-      <c r="AI67" s="2">
-        <v>5</v>
+      <c r="AI67" s="1">
+        <v>486</v>
       </c>
       <c r="AJ67" s="1">
         <v>1620</v>
@@ -5818,8 +5818,8 @@
       <c r="E68" t="str">
         <v/>
       </c>
-      <c r="F68" s="1">
-        <v>756</v>
+      <c r="F68" s="2">
+        <v>5</v>
       </c>
       <c r="G68" s="2">
         <v>5</v>
@@ -5900,13 +5900,13 @@
         <v>5</v>
       </c>
       <c r="AG68" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AH68" s="2">
         <v>135</v>
       </c>
-      <c r="AI68" s="2">
-        <v>11</v>
+      <c r="AI68" s="1">
+        <v>756</v>
       </c>
       <c r="AJ68" s="1">
         <v>2700</v>
@@ -5931,8 +5931,8 @@
       <c r="E69" s="1">
         <v>6</v>
       </c>
-      <c r="F69" s="1">
-        <v>486</v>
+      <c r="F69" s="2">
+        <v>3</v>
       </c>
       <c r="G69" s="2">
         <v>3</v>
@@ -6013,13 +6013,13 @@
         <v>3</v>
       </c>
       <c r="AG69" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH69" s="2">
         <v>81</v>
       </c>
-      <c r="AI69" s="2">
-        <v>6</v>
+      <c r="AI69" s="1">
+        <v>486</v>
       </c>
       <c r="AJ69" s="1">
         <v>1620</v>
@@ -6044,8 +6044,8 @@
       <c r="E70" s="1">
         <v>7</v>
       </c>
-      <c r="F70" s="1">
-        <v>189</v>
+      <c r="F70" s="2">
+        <v>1</v>
       </c>
       <c r="G70" s="2">
         <v>1</v>
@@ -6126,13 +6126,13 @@
         <v>1</v>
       </c>
       <c r="AG70" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH70" s="2">
         <v>27</v>
       </c>
-      <c r="AI70" s="2">
-        <v>6</v>
+      <c r="AI70" s="1">
+        <v>189</v>
       </c>
       <c r="AJ70" s="1">
         <v>540</v>
@@ -6157,8 +6157,8 @@
       <c r="E71" s="1">
         <v>8</v>
       </c>
-      <c r="F71" s="1">
-        <v>216</v>
+      <c r="F71" s="2">
+        <v>1</v>
       </c>
       <c r="G71" s="2">
         <v>1</v>
@@ -6239,13 +6239,13 @@
         <v>1</v>
       </c>
       <c r="AG71" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH71" s="2">
         <v>27</v>
       </c>
-      <c r="AI71" s="2">
-        <v>5</v>
+      <c r="AI71" s="1">
+        <v>216</v>
       </c>
       <c r="AJ71" s="1">
         <v>540</v>
@@ -6270,8 +6270,8 @@
       <c r="E72" t="str">
         <v/>
       </c>
-      <c r="F72" s="1">
-        <v>405</v>
+      <c r="F72" s="2">
+        <v>2</v>
       </c>
       <c r="G72" s="2">
         <v>2</v>
@@ -6352,13 +6352,13 @@
         <v>2</v>
       </c>
       <c r="AG72" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AH72" s="2">
         <v>54</v>
       </c>
-      <c r="AI72" s="2">
-        <v>11</v>
+      <c r="AI72" s="1">
+        <v>405</v>
       </c>
       <c r="AJ72" s="1">
         <v>1080</v>
@@ -6383,8 +6383,8 @@
       <c r="E73" s="1">
         <v>3</v>
       </c>
-      <c r="F73" s="1">
-        <v>162</v>
+      <c r="F73" s="2">
+        <v>2</v>
       </c>
       <c r="G73" s="2">
         <v>2</v>
@@ -6465,13 +6465,13 @@
         <v>2</v>
       </c>
       <c r="AG73" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH73" s="2">
         <v>54</v>
       </c>
-      <c r="AI73" s="2">
-        <v>6</v>
+      <c r="AI73" s="1">
+        <v>162</v>
       </c>
       <c r="AJ73" s="1">
         <v>1080</v>
@@ -6496,8 +6496,8 @@
       <c r="E74" s="1">
         <v>4</v>
       </c>
-      <c r="F74" s="1">
-        <v>324</v>
+      <c r="F74" s="2">
+        <v>3</v>
       </c>
       <c r="G74" s="2">
         <v>3</v>
@@ -6578,13 +6578,13 @@
         <v>3</v>
       </c>
       <c r="AG74" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH74" s="2">
         <v>81</v>
       </c>
-      <c r="AI74" s="2">
-        <v>6</v>
+      <c r="AI74" s="1">
+        <v>324</v>
       </c>
       <c r="AJ74" s="1">
         <v>1620</v>
@@ -6609,8 +6609,8 @@
       <c r="E75" s="1">
         <v>5</v>
       </c>
-      <c r="F75" s="1">
-        <v>405</v>
+      <c r="F75" s="2">
+        <v>3</v>
       </c>
       <c r="G75" s="2">
         <v>3</v>
@@ -6691,13 +6691,13 @@
         <v>3</v>
       </c>
       <c r="AG75" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH75" s="2">
         <v>81</v>
       </c>
-      <c r="AI75" s="2">
-        <v>5</v>
+      <c r="AI75" s="1">
+        <v>405</v>
       </c>
       <c r="AJ75" s="1">
         <v>1620</v>
@@ -6722,8 +6722,8 @@
       <c r="E76" t="str">
         <v/>
       </c>
-      <c r="F76" s="1">
-        <v>729</v>
+      <c r="F76" s="2">
+        <v>6</v>
       </c>
       <c r="G76" s="2">
         <v>6</v>
@@ -6804,13 +6804,13 @@
         <v>6</v>
       </c>
       <c r="AG76" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AH76" s="2">
         <v>162</v>
       </c>
-      <c r="AI76" s="2">
-        <v>11</v>
+      <c r="AI76" s="1">
+        <v>729</v>
       </c>
       <c r="AJ76" s="1">
         <v>3240</v>
@@ -6835,8 +6835,8 @@
       <c r="E77" s="1">
         <v>5</v>
       </c>
-      <c r="F77" s="1">
-        <v>135</v>
+      <c r="F77" s="2">
+        <v>1</v>
       </c>
       <c r="G77" s="2">
         <v>1</v>
@@ -6917,13 +6917,13 @@
         <v>1</v>
       </c>
       <c r="AG77" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH77" s="2">
         <v>27</v>
       </c>
-      <c r="AI77" s="2">
-        <v>6</v>
+      <c r="AI77" s="1">
+        <v>135</v>
       </c>
       <c r="AJ77" s="1">
         <v>540</v>
@@ -6948,8 +6948,8 @@
       <c r="E78" s="1">
         <v>6</v>
       </c>
-      <c r="F78" s="1">
-        <v>324</v>
+      <c r="F78" s="2">
+        <v>2</v>
       </c>
       <c r="G78" s="2">
         <v>2</v>
@@ -7030,13 +7030,13 @@
         <v>2</v>
       </c>
       <c r="AG78" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH78" s="2">
         <v>54</v>
       </c>
-      <c r="AI78" s="2">
-        <v>6</v>
+      <c r="AI78" s="1">
+        <v>324</v>
       </c>
       <c r="AJ78" s="1">
         <v>1080</v>
@@ -7061,8 +7061,8 @@
       <c r="E79" s="1">
         <v>7</v>
       </c>
-      <c r="F79" s="1">
-        <v>189</v>
+      <c r="F79" s="2">
+        <v>1</v>
       </c>
       <c r="G79" s="2">
         <v>1</v>
@@ -7143,13 +7143,13 @@
         <v>1</v>
       </c>
       <c r="AG79" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH79" s="2">
         <v>27</v>
       </c>
-      <c r="AI79" s="2">
-        <v>5</v>
+      <c r="AI79" s="1">
+        <v>189</v>
       </c>
       <c r="AJ79" s="1">
         <v>540</v>
@@ -7174,8 +7174,8 @@
       <c r="E80" t="str">
         <v/>
       </c>
-      <c r="F80" s="1">
-        <v>513</v>
+      <c r="F80" s="2">
+        <v>3</v>
       </c>
       <c r="G80" s="2">
         <v>3</v>
@@ -7256,13 +7256,13 @@
         <v>3</v>
       </c>
       <c r="AG80" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AH80" s="2">
         <v>81</v>
       </c>
-      <c r="AI80" s="2">
-        <v>11</v>
+      <c r="AI80" s="1">
+        <v>513</v>
       </c>
       <c r="AJ80" s="1">
         <v>1620</v>
@@ -7287,8 +7287,8 @@
       <c r="E81" s="1">
         <v>7</v>
       </c>
-      <c r="F81" s="1">
-        <v>567</v>
+      <c r="F81" s="2">
+        <v>3</v>
       </c>
       <c r="G81" s="2">
         <v>3</v>
@@ -7369,13 +7369,13 @@
         <v>3</v>
       </c>
       <c r="AG81" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH81" s="2">
         <v>81</v>
       </c>
-      <c r="AI81" s="2">
-        <v>6</v>
+      <c r="AI81" s="1">
+        <v>567</v>
       </c>
       <c r="AJ81" s="1">
         <v>1620</v>
@@ -7400,8 +7400,8 @@
       <c r="E82" s="1">
         <v>3</v>
       </c>
-      <c r="F82" s="1">
-        <v>81</v>
+      <c r="F82" s="2">
+        <v>1</v>
       </c>
       <c r="G82" s="2">
         <v>1</v>
@@ -7482,13 +7482,13 @@
         <v>1</v>
       </c>
       <c r="AG82" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH82" s="2">
         <v>27</v>
       </c>
-      <c r="AI82" s="2">
-        <v>6</v>
+      <c r="AI82" s="1">
+        <v>81</v>
       </c>
       <c r="AJ82" s="1">
         <v>540</v>
@@ -7513,8 +7513,8 @@
       <c r="E83" s="1">
         <v>4</v>
       </c>
-      <c r="F83" s="1">
-        <v>324</v>
+      <c r="F83" s="2">
+        <v>3</v>
       </c>
       <c r="G83" s="2">
         <v>3</v>
@@ -7595,13 +7595,13 @@
         <v>3</v>
       </c>
       <c r="AG83" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH83" s="2">
         <v>81</v>
       </c>
-      <c r="AI83" s="2">
-        <v>5</v>
+      <c r="AI83" s="1">
+        <v>324</v>
       </c>
       <c r="AJ83" s="1">
         <v>1620</v>
@@ -7626,8 +7626,8 @@
       <c r="E84" t="str">
         <v/>
       </c>
-      <c r="F84" s="1">
-        <v>405</v>
+      <c r="F84" s="2">
+        <v>4</v>
       </c>
       <c r="G84" s="2">
         <v>4</v>
@@ -7708,13 +7708,13 @@
         <v>4</v>
       </c>
       <c r="AG84" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH84" s="2">
         <v>108</v>
       </c>
-      <c r="AI84" s="2">
-        <v>11</v>
+      <c r="AI84" s="1">
+        <v>405</v>
       </c>
       <c r="AJ84" s="1">
         <v>2160</v>
@@ -7739,8 +7739,8 @@
       <c r="E85" s="1">
         <v>4</v>
       </c>
-      <c r="F85" s="1">
-        <v>216</v>
+      <c r="F85" s="2">
+        <v>2</v>
       </c>
       <c r="G85" s="2">
         <v>2</v>
@@ -7821,13 +7821,13 @@
         <v>2</v>
       </c>
       <c r="AG85" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH85" s="2">
         <v>54</v>
       </c>
-      <c r="AI85" s="2">
-        <v>6</v>
+      <c r="AI85" s="1">
+        <v>216</v>
       </c>
       <c r="AJ85" s="1">
         <v>1080</v>
@@ -7852,8 +7852,8 @@
       <c r="E86" s="1">
         <v>5</v>
       </c>
-      <c r="F86" s="1">
-        <v>405</v>
+      <c r="F86" s="2">
+        <v>3</v>
       </c>
       <c r="G86" s="2">
         <v>3</v>
@@ -7934,13 +7934,13 @@
         <v>3</v>
       </c>
       <c r="AG86" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH86" s="2">
         <v>81</v>
       </c>
-      <c r="AI86" s="2">
-        <v>6</v>
+      <c r="AI86" s="1">
+        <v>405</v>
       </c>
       <c r="AJ86" s="1">
         <v>1620</v>
@@ -7965,8 +7965,8 @@
       <c r="E87" s="1">
         <v>6</v>
       </c>
-      <c r="F87" s="1">
-        <v>162</v>
+      <c r="F87" s="2">
+        <v>1</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
@@ -8047,13 +8047,13 @@
         <v>1</v>
       </c>
       <c r="AG87" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH87" s="2">
         <v>27</v>
       </c>
-      <c r="AI87" s="2">
-        <v>5</v>
+      <c r="AI87" s="1">
+        <v>162</v>
       </c>
       <c r="AJ87" s="1">
         <v>540</v>
@@ -8078,8 +8078,8 @@
       <c r="E88" t="str">
         <v/>
       </c>
-      <c r="F88" s="1">
-        <v>567</v>
+      <c r="F88" s="2">
+        <v>4</v>
       </c>
       <c r="G88" s="2">
         <v>4</v>
@@ -8160,13 +8160,13 @@
         <v>4</v>
       </c>
       <c r="AG88" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH88" s="2">
         <v>108</v>
       </c>
-      <c r="AI88" s="2">
-        <v>11</v>
+      <c r="AI88" s="1">
+        <v>567</v>
       </c>
       <c r="AJ88" s="1">
         <v>2160</v>
@@ -8191,8 +8191,8 @@
       <c r="E89" s="1">
         <v>6</v>
       </c>
-      <c r="F89" s="1">
-        <v>162</v>
+      <c r="F89" s="2">
+        <v>1</v>
       </c>
       <c r="G89" s="2">
         <v>1</v>
@@ -8273,13 +8273,13 @@
         <v>1</v>
       </c>
       <c r="AG89" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH89" s="2">
         <v>27</v>
       </c>
-      <c r="AI89" s="2">
-        <v>6</v>
+      <c r="AI89" s="1">
+        <v>162</v>
       </c>
       <c r="AJ89" s="1">
         <v>540</v>
@@ -8304,8 +8304,8 @@
       <c r="E90" s="1">
         <v>7</v>
       </c>
-      <c r="F90" s="1">
-        <v>378</v>
+      <c r="F90" s="2">
+        <v>2</v>
       </c>
       <c r="G90" s="2">
         <v>2</v>
@@ -8386,13 +8386,13 @@
         <v>2</v>
       </c>
       <c r="AG90" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH90" s="2">
         <v>54</v>
       </c>
-      <c r="AI90" s="2">
-        <v>6</v>
+      <c r="AI90" s="1">
+        <v>378</v>
       </c>
       <c r="AJ90" s="1">
         <v>1080</v>
@@ -8417,8 +8417,8 @@
       <c r="E91" s="1">
         <v>8</v>
       </c>
-      <c r="F91" s="1">
-        <v>648</v>
+      <c r="F91" s="2">
+        <v>3</v>
       </c>
       <c r="G91" s="2">
         <v>3</v>
@@ -8499,13 +8499,13 @@
         <v>3</v>
       </c>
       <c r="AG91" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH91" s="2">
         <v>81</v>
       </c>
-      <c r="AI91" s="2">
-        <v>5</v>
+      <c r="AI91" s="1">
+        <v>648</v>
       </c>
       <c r="AJ91" s="1">
         <v>1620</v>
@@ -8530,8 +8530,8 @@
       <c r="E92" t="str">
         <v/>
       </c>
-      <c r="F92" s="1">
-        <v>1026</v>
+      <c r="F92" s="2">
+        <v>5</v>
       </c>
       <c r="G92" s="2">
         <v>5</v>
@@ -8612,13 +8612,13 @@
         <v>5</v>
       </c>
       <c r="AG92" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AH92" s="2">
         <v>135</v>
       </c>
-      <c r="AI92" s="2">
-        <v>11</v>
+      <c r="AI92" s="1">
+        <v>1026</v>
       </c>
       <c r="AJ92" s="1">
         <v>2700</v>
@@ -8643,8 +8643,8 @@
       <c r="E93" s="1">
         <v>3</v>
       </c>
-      <c r="F93" s="1">
-        <v>243</v>
+      <c r="F93" s="2">
+        <v>3</v>
       </c>
       <c r="G93" s="2">
         <v>3</v>
@@ -8725,13 +8725,13 @@
         <v>3</v>
       </c>
       <c r="AG93" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH93" s="2">
         <v>81</v>
       </c>
-      <c r="AI93" s="2">
-        <v>6</v>
+      <c r="AI93" s="1">
+        <v>243</v>
       </c>
       <c r="AJ93" s="1">
         <v>1620</v>
@@ -8756,8 +8756,8 @@
       <c r="E94" s="1">
         <v>4</v>
       </c>
-      <c r="F94" s="1">
-        <v>108</v>
+      <c r="F94" s="2">
+        <v>1</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -8838,13 +8838,13 @@
         <v>1</v>
       </c>
       <c r="AG94" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH94" s="2">
         <v>27</v>
       </c>
-      <c r="AI94" s="2">
-        <v>0</v>
+      <c r="AI94" s="1">
+        <v>108</v>
       </c>
       <c r="AJ94" s="1">
         <v>540</v>
@@ -8869,8 +8869,8 @@
       <c r="E95" s="1">
         <v>5</v>
       </c>
-      <c r="F95" s="1">
-        <v>135</v>
+      <c r="F95" s="2">
+        <v>1</v>
       </c>
       <c r="G95" s="2">
         <v>1</v>
@@ -8951,13 +8951,13 @@
         <v>1</v>
       </c>
       <c r="AG95" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH95" s="2">
         <v>27</v>
       </c>
-      <c r="AI95" s="2">
-        <v>5</v>
+      <c r="AI95" s="1">
+        <v>135</v>
       </c>
       <c r="AJ95" s="1">
         <v>540</v>
@@ -8982,8 +8982,8 @@
       <c r="E96" t="str">
         <v/>
       </c>
-      <c r="F96" s="1">
-        <v>243</v>
+      <c r="F96" s="2">
+        <v>2</v>
       </c>
       <c r="G96" s="2">
         <v>2</v>
@@ -9064,13 +9064,13 @@
         <v>2</v>
       </c>
       <c r="AG96" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH96" s="2">
         <v>54</v>
       </c>
-      <c r="AI96" s="2">
-        <v>5</v>
+      <c r="AI96" s="1">
+        <v>243</v>
       </c>
       <c r="AJ96" s="1">
         <v>1080</v>
@@ -9095,8 +9095,8 @@
       <c r="E97" s="1">
         <v>5</v>
       </c>
-      <c r="F97" s="1">
-        <v>270</v>
+      <c r="F97" s="2">
+        <v>2</v>
       </c>
       <c r="G97" s="2">
         <v>2</v>
@@ -9177,13 +9177,13 @@
         <v>2</v>
       </c>
       <c r="AG97" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH97" s="2">
         <v>54</v>
       </c>
-      <c r="AI97" s="2">
-        <v>6</v>
+      <c r="AI97" s="1">
+        <v>270</v>
       </c>
       <c r="AJ97" s="1">
         <v>1080</v>
@@ -9208,8 +9208,8 @@
       <c r="E98" s="1">
         <v>6</v>
       </c>
-      <c r="F98" s="1">
-        <v>486</v>
+      <c r="F98" s="2">
+        <v>3</v>
       </c>
       <c r="G98" s="2">
         <v>3</v>
@@ -9290,13 +9290,13 @@
         <v>3</v>
       </c>
       <c r="AG98" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH98" s="2">
         <v>81</v>
       </c>
-      <c r="AI98" s="2">
-        <v>6</v>
+      <c r="AI98" s="1">
+        <v>486</v>
       </c>
       <c r="AJ98" s="1">
         <v>1620</v>
@@ -9321,8 +9321,8 @@
       <c r="E99" s="1">
         <v>7</v>
       </c>
-      <c r="F99" s="1">
-        <v>567</v>
+      <c r="F99" s="2">
+        <v>3</v>
       </c>
       <c r="G99" s="2">
         <v>3</v>
@@ -9403,13 +9403,13 @@
         <v>3</v>
       </c>
       <c r="AG99" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH99" s="2">
         <v>81</v>
       </c>
-      <c r="AI99" s="2">
-        <v>5</v>
+      <c r="AI99" s="1">
+        <v>567</v>
       </c>
       <c r="AJ99" s="1">
         <v>1620</v>
@@ -9434,8 +9434,8 @@
       <c r="E100" t="str">
         <v/>
       </c>
-      <c r="F100" s="1">
-        <v>1053</v>
+      <c r="F100" s="2">
+        <v>6</v>
       </c>
       <c r="G100" s="2">
         <v>6</v>
@@ -9516,13 +9516,13 @@
         <v>6</v>
       </c>
       <c r="AG100" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AH100" s="2">
         <v>162</v>
       </c>
-      <c r="AI100" s="2">
-        <v>11</v>
+      <c r="AI100" s="1">
+        <v>1053</v>
       </c>
       <c r="AJ100" s="1">
         <v>3240</v>
@@ -9547,8 +9547,8 @@
       <c r="E101" s="1">
         <v>7</v>
       </c>
-      <c r="F101" s="1">
-        <v>189</v>
+      <c r="F101" s="2">
+        <v>1</v>
       </c>
       <c r="G101" s="2">
         <v>1</v>
@@ -9629,13 +9629,13 @@
         <v>1</v>
       </c>
       <c r="AG101" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH101" s="2">
         <v>27</v>
       </c>
-      <c r="AI101" s="2">
-        <v>6</v>
+      <c r="AI101" s="1">
+        <v>189</v>
       </c>
       <c r="AJ101" s="1">
         <v>540</v>
@@ -9660,8 +9660,8 @@
       <c r="E102" s="1">
         <v>3</v>
       </c>
-      <c r="F102" s="1">
-        <v>162</v>
+      <c r="F102" s="2">
+        <v>2</v>
       </c>
       <c r="G102" s="2">
         <v>2</v>
@@ -9742,13 +9742,13 @@
         <v>2</v>
       </c>
       <c r="AG102" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH102" s="2">
         <v>54</v>
       </c>
-      <c r="AI102" s="2">
-        <v>6</v>
+      <c r="AI102" s="1">
+        <v>162</v>
       </c>
       <c r="AJ102" s="1">
         <v>1080</v>
@@ -9773,8 +9773,8 @@
       <c r="E103" s="1">
         <v>4</v>
       </c>
-      <c r="F103" s="1">
-        <v>108</v>
+      <c r="F103" s="2">
+        <v>1</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -9855,13 +9855,13 @@
         <v>1</v>
       </c>
       <c r="AG103" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH103" s="2">
         <v>27</v>
       </c>
-      <c r="AI103" s="2">
-        <v>5</v>
+      <c r="AI103" s="1">
+        <v>108</v>
       </c>
       <c r="AJ103" s="1">
         <v>540</v>
@@ -9886,8 +9886,8 @@
       <c r="E104" t="str">
         <v/>
       </c>
-      <c r="F104" s="1">
-        <v>270</v>
+      <c r="F104" s="2">
+        <v>3</v>
       </c>
       <c r="G104" s="2">
         <v>3</v>
@@ -9968,13 +9968,13 @@
         <v>3</v>
       </c>
       <c r="AG104" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AH104" s="2">
         <v>81</v>
       </c>
-      <c r="AI104" s="2">
-        <v>11</v>
+      <c r="AI104" s="1">
+        <v>270</v>
       </c>
       <c r="AJ104" s="1">
         <v>1620</v>
@@ -9999,8 +9999,8 @@
       <c r="E105" s="1">
         <v>4</v>
       </c>
-      <c r="F105" s="1">
-        <v>324</v>
+      <c r="F105" s="2">
+        <v>3</v>
       </c>
       <c r="G105" s="2">
         <v>3</v>
@@ -10081,13 +10081,13 @@
         <v>3</v>
       </c>
       <c r="AG105" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH105" s="2">
         <v>81</v>
       </c>
-      <c r="AI105" s="2">
-        <v>6</v>
+      <c r="AI105" s="1">
+        <v>324</v>
       </c>
       <c r="AJ105" s="1">
         <v>1620</v>
@@ -10112,8 +10112,8 @@
       <c r="E106" s="1">
         <v>5</v>
       </c>
-      <c r="F106" s="1">
-        <v>135</v>
+      <c r="F106" s="2">
+        <v>1</v>
       </c>
       <c r="G106" s="2">
         <v>1</v>
@@ -10194,13 +10194,13 @@
         <v>1</v>
       </c>
       <c r="AG106" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH106" s="2">
         <v>27</v>
       </c>
-      <c r="AI106" s="2">
-        <v>6</v>
+      <c r="AI106" s="1">
+        <v>135</v>
       </c>
       <c r="AJ106" s="1">
         <v>540</v>
@@ -10225,8 +10225,8 @@
       <c r="E107" s="1">
         <v>6</v>
       </c>
-      <c r="F107" s="1">
-        <v>486</v>
+      <c r="F107" s="2">
+        <v>3</v>
       </c>
       <c r="G107" s="2">
         <v>3</v>
@@ -10307,13 +10307,13 @@
         <v>3</v>
       </c>
       <c r="AG107" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH107" s="2">
         <v>81</v>
       </c>
-      <c r="AI107" s="2">
-        <v>5</v>
+      <c r="AI107" s="1">
+        <v>486</v>
       </c>
       <c r="AJ107" s="1">
         <v>1620</v>
@@ -10338,8 +10338,8 @@
       <c r="E108" t="str">
         <v/>
       </c>
-      <c r="F108" s="1">
-        <v>621</v>
+      <c r="F108" s="2">
+        <v>4</v>
       </c>
       <c r="G108" s="2">
         <v>4</v>
@@ -10420,13 +10420,13 @@
         <v>4</v>
       </c>
       <c r="AG108" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH108" s="2">
         <v>108</v>
       </c>
-      <c r="AI108" s="2">
-        <v>11</v>
+      <c r="AI108" s="1">
+        <v>621</v>
       </c>
       <c r="AJ108" s="1">
         <v>2160</v>
@@ -10451,8 +10451,8 @@
       <c r="E109" s="1">
         <v>6</v>
       </c>
-      <c r="F109" s="1">
-        <v>324</v>
+      <c r="F109" s="2">
+        <v>2</v>
       </c>
       <c r="G109" s="2">
         <v>2</v>
@@ -10533,13 +10533,13 @@
         <v>2</v>
       </c>
       <c r="AG109" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH109" s="2">
         <v>54</v>
       </c>
-      <c r="AI109" s="2">
-        <v>6</v>
+      <c r="AI109" s="1">
+        <v>324</v>
       </c>
       <c r="AJ109" s="1">
         <v>1080</v>
@@ -10564,8 +10564,8 @@
       <c r="E110" s="1">
         <v>7</v>
       </c>
-      <c r="F110" s="1">
-        <v>567</v>
+      <c r="F110" s="2">
+        <v>3</v>
       </c>
       <c r="G110" s="2">
         <v>3</v>
@@ -10646,13 +10646,13 @@
         <v>3</v>
       </c>
       <c r="AG110" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH110" s="2">
         <v>81</v>
       </c>
-      <c r="AI110" s="2">
-        <v>6</v>
+      <c r="AI110" s="1">
+        <v>567</v>
       </c>
       <c r="AJ110" s="1">
         <v>1620</v>
@@ -10677,8 +10677,8 @@
       <c r="E111" s="1">
         <v>8</v>
       </c>
-      <c r="F111" s="1">
-        <v>216</v>
+      <c r="F111" s="2">
+        <v>1</v>
       </c>
       <c r="G111" s="2">
         <v>1</v>
@@ -10759,13 +10759,13 @@
         <v>1</v>
       </c>
       <c r="AG111" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH111" s="2">
         <v>27</v>
       </c>
-      <c r="AI111" s="2">
-        <v>5</v>
+      <c r="AI111" s="1">
+        <v>216</v>
       </c>
       <c r="AJ111" s="1">
         <v>540</v>
@@ -10790,8 +10790,8 @@
       <c r="E112" t="str">
         <v/>
       </c>
-      <c r="F112" s="1">
-        <v>783</v>
+      <c r="F112" s="2">
+        <v>4</v>
       </c>
       <c r="G112" s="2">
         <v>4</v>
@@ -10872,13 +10872,13 @@
         <v>4</v>
       </c>
       <c r="AG112" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH112" s="2">
         <v>108</v>
       </c>
-      <c r="AI112" s="2">
-        <v>11</v>
+      <c r="AI112" s="1">
+        <v>783</v>
       </c>
       <c r="AJ112" s="1">
         <v>2160</v>
@@ -10903,8 +10903,8 @@
       <c r="E113" s="1">
         <v>3</v>
       </c>
-      <c r="F113" s="1">
-        <v>81</v>
+      <c r="F113" s="2">
+        <v>1</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -10985,13 +10985,13 @@
         <v>1</v>
       </c>
       <c r="AG113" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH113" s="2">
         <v>27</v>
       </c>
-      <c r="AI113" s="2">
-        <v>6</v>
+      <c r="AI113" s="1">
+        <v>81</v>
       </c>
       <c r="AJ113" s="1">
         <v>540</v>
@@ -11016,8 +11016,8 @@
       <c r="E114" s="1">
         <v>4</v>
       </c>
-      <c r="F114" s="1">
-        <v>216</v>
+      <c r="F114" s="2">
+        <v>2</v>
       </c>
       <c r="G114" s="2">
         <v>2</v>
@@ -11098,13 +11098,13 @@
         <v>2</v>
       </c>
       <c r="AG114" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH114" s="2">
         <v>54</v>
       </c>
-      <c r="AI114" s="2">
-        <v>6</v>
+      <c r="AI114" s="1">
+        <v>216</v>
       </c>
       <c r="AJ114" s="1">
         <v>1080</v>
@@ -11129,8 +11129,8 @@
       <c r="E115" s="1">
         <v>5</v>
       </c>
-      <c r="F115" s="1">
-        <v>405</v>
+      <c r="F115" s="2">
+        <v>3</v>
       </c>
       <c r="G115" s="2">
         <v>3</v>
@@ -11211,13 +11211,13 @@
         <v>3</v>
       </c>
       <c r="AG115" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH115" s="2">
         <v>81</v>
       </c>
-      <c r="AI115" s="2">
-        <v>5</v>
+      <c r="AI115" s="1">
+        <v>405</v>
       </c>
       <c r="AJ115" s="1">
         <v>1620</v>
@@ -11242,8 +11242,8 @@
       <c r="E116" t="str">
         <v/>
       </c>
-      <c r="F116" s="1">
-        <v>621</v>
+      <c r="F116" s="2">
+        <v>5</v>
       </c>
       <c r="G116" s="2">
         <v>5</v>
@@ -11324,13 +11324,13 @@
         <v>5</v>
       </c>
       <c r="AG116" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AH116" s="2">
         <v>135</v>
       </c>
-      <c r="AI116" s="2">
-        <v>11</v>
+      <c r="AI116" s="1">
+        <v>621</v>
       </c>
       <c r="AJ116" s="1">
         <v>2700</v>
@@ -11355,8 +11355,8 @@
       <c r="E117" s="1">
         <v>5</v>
       </c>
-      <c r="F117" s="1">
-        <v>405</v>
+      <c r="F117" s="2">
+        <v>3</v>
       </c>
       <c r="G117" s="2">
         <v>3</v>
@@ -11437,13 +11437,13 @@
         <v>3</v>
       </c>
       <c r="AG117" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH117" s="2">
         <v>81</v>
       </c>
-      <c r="AI117" s="2">
-        <v>6</v>
+      <c r="AI117" s="1">
+        <v>405</v>
       </c>
       <c r="AJ117" s="1">
         <v>1620</v>
@@ -11468,8 +11468,8 @@
       <c r="E118" s="1">
         <v>6</v>
       </c>
-      <c r="F118" s="1">
-        <v>162</v>
+      <c r="F118" s="2">
+        <v>1</v>
       </c>
       <c r="G118" s="2">
         <v>1</v>
@@ -11550,13 +11550,13 @@
         <v>1</v>
       </c>
       <c r="AG118" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH118" s="2">
         <v>27</v>
       </c>
-      <c r="AI118" s="2">
-        <v>6</v>
+      <c r="AI118" s="1">
+        <v>162</v>
       </c>
       <c r="AJ118" s="1">
         <v>540</v>
@@ -11581,8 +11581,8 @@
       <c r="E119" s="1">
         <v>7</v>
       </c>
-      <c r="F119" s="1">
-        <v>189</v>
+      <c r="F119" s="2">
+        <v>1</v>
       </c>
       <c r="G119" s="2">
         <v>1</v>
@@ -11663,13 +11663,13 @@
         <v>1</v>
       </c>
       <c r="AG119" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH119" s="2">
         <v>27</v>
       </c>
-      <c r="AI119" s="2">
-        <v>5</v>
+      <c r="AI119" s="1">
+        <v>189</v>
       </c>
       <c r="AJ119" s="1">
         <v>540</v>
@@ -11694,8 +11694,8 @@
       <c r="E120" t="str">
         <v/>
       </c>
-      <c r="F120" s="1">
-        <v>351</v>
+      <c r="F120" s="2">
+        <v>2</v>
       </c>
       <c r="G120" s="2">
         <v>2</v>
@@ -11776,13 +11776,13 @@
         <v>2</v>
       </c>
       <c r="AG120" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AH120" s="2">
         <v>54</v>
       </c>
-      <c r="AI120" s="2">
-        <v>11</v>
+      <c r="AI120" s="1">
+        <v>351</v>
       </c>
       <c r="AJ120" s="1">
         <v>1080</v>
@@ -11807,8 +11807,8 @@
       <c r="E121" s="1">
         <v>7</v>
       </c>
-      <c r="F121" s="1">
-        <v>378</v>
+      <c r="F121" s="2">
+        <v>2</v>
       </c>
       <c r="G121" s="2">
         <v>2</v>
@@ -11889,13 +11889,13 @@
         <v>2</v>
       </c>
       <c r="AG121" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH121" s="2">
         <v>54</v>
       </c>
-      <c r="AI121" s="2">
-        <v>6</v>
+      <c r="AI121" s="1">
+        <v>378</v>
       </c>
       <c r="AJ121" s="1">
         <v>1080</v>
@@ -11920,8 +11920,8 @@
       <c r="E122" s="1">
         <v>3</v>
       </c>
-      <c r="F122" s="1">
-        <v>243</v>
+      <c r="F122" s="2">
+        <v>3</v>
       </c>
       <c r="G122" s="2">
         <v>3</v>
@@ -12002,13 +12002,13 @@
         <v>3</v>
       </c>
       <c r="AG122" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH122" s="2">
         <v>81</v>
       </c>
-      <c r="AI122" s="2">
-        <v>6</v>
+      <c r="AI122" s="1">
+        <v>243</v>
       </c>
       <c r="AJ122" s="1">
         <v>1620</v>
@@ -12033,8 +12033,8 @@
       <c r="E123" s="1">
         <v>4</v>
       </c>
-      <c r="F123" s="1">
-        <v>324</v>
+      <c r="F123" s="2">
+        <v>3</v>
       </c>
       <c r="G123" s="2">
         <v>3</v>
@@ -12115,13 +12115,13 @@
         <v>3</v>
       </c>
       <c r="AG123" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH123" s="2">
         <v>81</v>
       </c>
-      <c r="AI123" s="2">
-        <v>5</v>
+      <c r="AI123" s="1">
+        <v>324</v>
       </c>
       <c r="AJ123" s="1">
         <v>1620</v>
@@ -12146,8 +12146,8 @@
       <c r="E124" t="str">
         <v/>
       </c>
-      <c r="F124" s="1">
-        <v>567</v>
+      <c r="F124" s="2">
+        <v>6</v>
       </c>
       <c r="G124" s="2">
         <v>6</v>
@@ -12228,13 +12228,13 @@
         <v>6</v>
       </c>
       <c r="AG124" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AH124" s="2">
         <v>162</v>
       </c>
-      <c r="AI124" s="2">
-        <v>11</v>
+      <c r="AI124" s="1">
+        <v>567</v>
       </c>
       <c r="AJ124" s="1">
         <v>3240</v>
@@ -12259,8 +12259,8 @@
       <c r="E125" s="1">
         <v>4</v>
       </c>
-      <c r="F125" s="1">
-        <v>108</v>
+      <c r="F125" s="2">
+        <v>1</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -12341,13 +12341,13 @@
         <v>1</v>
       </c>
       <c r="AG125" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH125" s="2">
         <v>27</v>
       </c>
-      <c r="AI125" s="2">
-        <v>6</v>
+      <c r="AI125" s="1">
+        <v>108</v>
       </c>
       <c r="AJ125" s="1">
         <v>540</v>
@@ -12372,8 +12372,8 @@
       <c r="E126" s="1">
         <v>5</v>
       </c>
-      <c r="F126" s="1">
-        <v>270</v>
+      <c r="F126" s="2">
+        <v>2</v>
       </c>
       <c r="G126" s="2">
         <v>2</v>
@@ -12454,13 +12454,13 @@
         <v>2</v>
       </c>
       <c r="AG126" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH126" s="2">
         <v>54</v>
       </c>
-      <c r="AI126" s="2">
-        <v>6</v>
+      <c r="AI126" s="1">
+        <v>270</v>
       </c>
       <c r="AJ126" s="1">
         <v>1080</v>
@@ -12485,8 +12485,8 @@
       <c r="E127" s="1">
         <v>6</v>
       </c>
-      <c r="F127" s="1">
-        <v>162</v>
+      <c r="F127" s="2">
+        <v>1</v>
       </c>
       <c r="G127" s="2">
         <v>1</v>
@@ -12567,13 +12567,13 @@
         <v>1</v>
       </c>
       <c r="AG127" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH127" s="2">
         <v>27</v>
       </c>
-      <c r="AI127" s="2">
-        <v>5</v>
+      <c r="AI127" s="1">
+        <v>162</v>
       </c>
       <c r="AJ127" s="1">
         <v>540</v>
@@ -12598,8 +12598,8 @@
       <c r="E128" t="str">
         <v/>
       </c>
-      <c r="F128" s="1">
-        <v>432</v>
+      <c r="F128" s="2">
+        <v>3</v>
       </c>
       <c r="G128" s="2">
         <v>3</v>
@@ -12680,13 +12680,13 @@
         <v>3</v>
       </c>
       <c r="AG128" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AH128" s="2">
         <v>81</v>
       </c>
-      <c r="AI128" s="2">
-        <v>11</v>
+      <c r="AI128" s="1">
+        <v>432</v>
       </c>
       <c r="AJ128" s="1">
         <v>1620</v>
@@ -12711,8 +12711,8 @@
       <c r="E129" s="1">
         <v>6</v>
       </c>
-      <c r="F129" s="1">
-        <v>486</v>
+      <c r="F129" s="2">
+        <v>3</v>
       </c>
       <c r="G129" s="2">
         <v>3</v>
@@ -12793,13 +12793,13 @@
         <v>3</v>
       </c>
       <c r="AG129" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH129" s="2">
         <v>81</v>
       </c>
-      <c r="AI129" s="2">
-        <v>6</v>
+      <c r="AI129" s="1">
+        <v>486</v>
       </c>
       <c r="AJ129" s="1">
         <v>1620</v>
@@ -12824,8 +12824,8 @@
       <c r="E130" s="1">
         <v>7</v>
       </c>
-      <c r="F130" s="1">
-        <v>189</v>
+      <c r="F130" s="2">
+        <v>1</v>
       </c>
       <c r="G130" s="2">
         <v>1</v>
@@ -12906,13 +12906,13 @@
         <v>1</v>
       </c>
       <c r="AG130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH130" s="2">
         <v>27</v>
       </c>
-      <c r="AI130" s="2">
-        <v>0</v>
+      <c r="AI130" s="1">
+        <v>189</v>
       </c>
       <c r="AJ130" s="1">
         <v>540</v>
@@ -12937,8 +12937,8 @@
       <c r="E131" s="1">
         <v>8</v>
       </c>
-      <c r="F131" s="1">
-        <v>648</v>
+      <c r="F131" s="2">
+        <v>3</v>
       </c>
       <c r="G131" s="2">
         <v>3</v>
@@ -13019,13 +13019,13 @@
         <v>3</v>
       </c>
       <c r="AG131" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH131" s="2">
         <v>81</v>
       </c>
-      <c r="AI131" s="2">
-        <v>5</v>
+      <c r="AI131" s="1">
+        <v>648</v>
       </c>
       <c r="AJ131" s="1">
         <v>1620</v>
@@ -13050,8 +13050,8 @@
       <c r="E132" t="str">
         <v/>
       </c>
-      <c r="F132" s="1">
-        <v>837</v>
+      <c r="F132" s="2">
+        <v>4</v>
       </c>
       <c r="G132" s="2">
         <v>4</v>
@@ -13132,13 +13132,13 @@
         <v>4</v>
       </c>
       <c r="AG132" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH132" s="2">
         <v>108</v>
       </c>
-      <c r="AI132" s="2">
-        <v>5</v>
+      <c r="AI132" s="1">
+        <v>837</v>
       </c>
       <c r="AJ132" s="1">
         <v>2160</v>
@@ -13163,8 +13163,8 @@
       <c r="E133" s="1">
         <v>3</v>
       </c>
-      <c r="F133" s="1">
-        <v>162</v>
+      <c r="F133" s="2">
+        <v>2</v>
       </c>
       <c r="G133" s="2">
         <v>2</v>
@@ -13245,13 +13245,13 @@
         <v>2</v>
       </c>
       <c r="AG133" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH133" s="2">
         <v>54</v>
       </c>
-      <c r="AI133" s="2">
-        <v>6</v>
+      <c r="AI133" s="1">
+        <v>162</v>
       </c>
       <c r="AJ133" s="1">
         <v>1080</v>
@@ -13276,8 +13276,8 @@
       <c r="E134" s="1">
         <v>4</v>
       </c>
-      <c r="F134" s="1">
-        <v>324</v>
+      <c r="F134" s="2">
+        <v>3</v>
       </c>
       <c r="G134" s="2">
         <v>3</v>
@@ -13358,13 +13358,13 @@
         <v>3</v>
       </c>
       <c r="AG134" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH134" s="2">
         <v>81</v>
       </c>
-      <c r="AI134" s="2">
-        <v>6</v>
+      <c r="AI134" s="1">
+        <v>324</v>
       </c>
       <c r="AJ134" s="1">
         <v>1620</v>
@@ -13389,8 +13389,8 @@
       <c r="E135" s="1">
         <v>5</v>
       </c>
-      <c r="F135" s="1">
-        <v>135</v>
+      <c r="F135" s="2">
+        <v>1</v>
       </c>
       <c r="G135" s="2">
         <v>1</v>
@@ -13471,13 +13471,13 @@
         <v>1</v>
       </c>
       <c r="AG135" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH135" s="2">
         <v>27</v>
       </c>
-      <c r="AI135" s="2">
-        <v>5</v>
+      <c r="AI135" s="1">
+        <v>135</v>
       </c>
       <c r="AJ135" s="1">
         <v>540</v>
@@ -13502,8 +13502,8 @@
       <c r="E136" t="str">
         <v/>
       </c>
-      <c r="F136" s="1">
-        <v>459</v>
+      <c r="F136" s="2">
+        <v>4</v>
       </c>
       <c r="G136" s="2">
         <v>4</v>
@@ -13584,13 +13584,13 @@
         <v>4</v>
       </c>
       <c r="AG136" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH136" s="2">
         <v>108</v>
       </c>
-      <c r="AI136" s="2">
-        <v>11</v>
+      <c r="AI136" s="1">
+        <v>459</v>
       </c>
       <c r="AJ136" s="1">
         <v>2160</v>
@@ -13615,8 +13615,8 @@
       <c r="E137" s="1">
         <v>5</v>
       </c>
-      <c r="F137" s="1">
-        <v>135</v>
+      <c r="F137" s="2">
+        <v>1</v>
       </c>
       <c r="G137" s="2">
         <v>1</v>
@@ -13697,13 +13697,13 @@
         <v>1</v>
       </c>
       <c r="AG137" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH137" s="2">
         <v>27</v>
       </c>
-      <c r="AI137" s="2">
-        <v>6</v>
+      <c r="AI137" s="1">
+        <v>135</v>
       </c>
       <c r="AJ137" s="1">
         <v>540</v>
@@ -13728,8 +13728,8 @@
       <c r="E138" s="1">
         <v>6</v>
       </c>
-      <c r="F138" s="1">
-        <v>324</v>
+      <c r="F138" s="2">
+        <v>2</v>
       </c>
       <c r="G138" s="2">
         <v>2</v>
@@ -13810,13 +13810,13 @@
         <v>2</v>
       </c>
       <c r="AG138" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH138" s="2">
         <v>54</v>
       </c>
-      <c r="AI138" s="2">
-        <v>6</v>
+      <c r="AI138" s="1">
+        <v>324</v>
       </c>
       <c r="AJ138" s="1">
         <v>1080</v>
@@ -13841,8 +13841,8 @@
       <c r="E139" s="1">
         <v>7</v>
       </c>
-      <c r="F139" s="1">
-        <v>567</v>
+      <c r="F139" s="2">
+        <v>3</v>
       </c>
       <c r="G139" s="2">
         <v>3</v>
@@ -13923,13 +13923,13 @@
         <v>3</v>
       </c>
       <c r="AG139" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH139" s="2">
         <v>81</v>
       </c>
-      <c r="AI139" s="2">
-        <v>5</v>
+      <c r="AI139" s="1">
+        <v>567</v>
       </c>
       <c r="AJ139" s="1">
         <v>1620</v>
@@ -13954,8 +13954,8 @@
       <c r="E140" t="str">
         <v/>
       </c>
-      <c r="F140" s="1">
-        <v>891</v>
+      <c r="F140" s="2">
+        <v>5</v>
       </c>
       <c r="G140" s="2">
         <v>5</v>
@@ -14036,13 +14036,13 @@
         <v>5</v>
       </c>
       <c r="AG140" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AH140" s="2">
         <v>135</v>
       </c>
-      <c r="AI140" s="2">
-        <v>11</v>
+      <c r="AI140" s="1">
+        <v>891</v>
       </c>
       <c r="AJ140" s="1">
         <v>2700</v>
@@ -14067,8 +14067,8 @@
       <c r="E141" s="1">
         <v>7</v>
       </c>
-      <c r="F141" s="1">
-        <v>567</v>
+      <c r="F141" s="2">
+        <v>3</v>
       </c>
       <c r="G141" s="2">
         <v>3</v>
@@ -14149,13 +14149,13 @@
         <v>3</v>
       </c>
       <c r="AG141" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH141" s="2">
         <v>81</v>
       </c>
-      <c r="AI141" s="2">
-        <v>6</v>
+      <c r="AI141" s="1">
+        <v>567</v>
       </c>
       <c r="AJ141" s="1">
         <v>1620</v>
@@ -14180,8 +14180,8 @@
       <c r="E142" s="1">
         <v>3</v>
       </c>
-      <c r="F142" s="1">
-        <v>81</v>
+      <c r="F142" s="2">
+        <v>1</v>
       </c>
       <c r="G142" s="2">
         <v>1</v>
@@ -14262,13 +14262,13 @@
         <v>1</v>
       </c>
       <c r="AG142" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH142" s="2">
         <v>27</v>
       </c>
-      <c r="AI142" s="2">
-        <v>6</v>
+      <c r="AI142" s="1">
+        <v>81</v>
       </c>
       <c r="AJ142" s="1">
         <v>540</v>
@@ -14293,8 +14293,8 @@
       <c r="E143" s="1">
         <v>4</v>
       </c>
-      <c r="F143" s="1">
-        <v>108</v>
+      <c r="F143" s="2">
+        <v>1</v>
       </c>
       <c r="G143" s="2">
         <v>1</v>
@@ -14375,13 +14375,13 @@
         <v>1</v>
       </c>
       <c r="AG143" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH143" s="2">
         <v>27</v>
       </c>
-      <c r="AI143" s="2">
-        <v>5</v>
+      <c r="AI143" s="1">
+        <v>108</v>
       </c>
       <c r="AJ143" s="1">
         <v>540</v>
@@ -14406,8 +14406,8 @@
       <c r="E144" t="str">
         <v/>
       </c>
-      <c r="F144" s="1">
-        <v>189</v>
+      <c r="F144" s="2">
+        <v>2</v>
       </c>
       <c r="G144" s="2">
         <v>2</v>
@@ -14488,13 +14488,13 @@
         <v>2</v>
       </c>
       <c r="AG144" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AH144" s="2">
         <v>54</v>
       </c>
-      <c r="AI144" s="2">
-        <v>11</v>
+      <c r="AI144" s="1">
+        <v>189</v>
       </c>
       <c r="AJ144" s="1">
         <v>1080</v>
@@ -14519,95 +14519,95 @@
       <c r="E145" s="1">
         <v>10000</v>
       </c>
-      <c r="F145" s="1">
+      <c r="F145" s="2">
+        <v>0</v>
+      </c>
+      <c r="G145" s="2">
+        <v>0</v>
+      </c>
+      <c r="H145" s="2">
+        <v>0</v>
+      </c>
+      <c r="I145" s="2">
+        <v>0</v>
+      </c>
+      <c r="J145" s="2">
+        <v>0</v>
+      </c>
+      <c r="K145" s="2">
+        <v>0</v>
+      </c>
+      <c r="L145" s="2">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2">
+        <v>0</v>
+      </c>
+      <c r="N145" s="2">
+        <v>0</v>
+      </c>
+      <c r="O145" s="2">
+        <v>0</v>
+      </c>
+      <c r="P145" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="2">
+        <v>0</v>
+      </c>
+      <c r="R145" s="2">
+        <v>0</v>
+      </c>
+      <c r="S145" s="2">
+        <v>0</v>
+      </c>
+      <c r="T145" s="2">
+        <v>0</v>
+      </c>
+      <c r="U145" s="2">
+        <v>0</v>
+      </c>
+      <c r="V145" s="2">
+        <v>0</v>
+      </c>
+      <c r="W145" s="2">
+        <v>0</v>
+      </c>
+      <c r="X145" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y145" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB145" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC145" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD145" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE145" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF145" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG145" s="2">
+        <v>3</v>
+      </c>
+      <c r="AH145" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI145" s="1">
         <v>10000</v>
-      </c>
-      <c r="G145" s="2">
-        <v>0</v>
-      </c>
-      <c r="H145" s="2">
-        <v>0</v>
-      </c>
-      <c r="I145" s="2">
-        <v>0</v>
-      </c>
-      <c r="J145" s="2">
-        <v>0</v>
-      </c>
-      <c r="K145" s="2">
-        <v>0</v>
-      </c>
-      <c r="L145" s="2">
-        <v>0</v>
-      </c>
-      <c r="M145" s="2">
-        <v>0</v>
-      </c>
-      <c r="N145" s="2">
-        <v>0</v>
-      </c>
-      <c r="O145" s="2">
-        <v>0</v>
-      </c>
-      <c r="P145" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q145" s="2">
-        <v>0</v>
-      </c>
-      <c r="R145" s="2">
-        <v>0</v>
-      </c>
-      <c r="S145" s="2">
-        <v>0</v>
-      </c>
-      <c r="T145" s="2">
-        <v>0</v>
-      </c>
-      <c r="U145" s="2">
-        <v>0</v>
-      </c>
-      <c r="V145" s="2">
-        <v>0</v>
-      </c>
-      <c r="W145" s="2">
-        <v>0</v>
-      </c>
-      <c r="X145" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y145" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z145" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA145" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB145" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC145" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD145" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE145" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF145" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG145" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH145" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI145" s="2">
-        <v>3</v>
       </c>
       <c r="AJ145" s="1">
         <v>20</v>
@@ -14632,95 +14632,95 @@
       <c r="E146" s="1">
         <v>10000</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F146" s="2">
+        <v>0</v>
+      </c>
+      <c r="G146" s="2">
+        <v>0</v>
+      </c>
+      <c r="H146" s="2">
+        <v>0</v>
+      </c>
+      <c r="I146" s="2">
+        <v>0</v>
+      </c>
+      <c r="J146" s="2">
+        <v>0</v>
+      </c>
+      <c r="K146" s="2">
+        <v>0</v>
+      </c>
+      <c r="L146" s="2">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2">
+        <v>0</v>
+      </c>
+      <c r="N146" s="2">
+        <v>0</v>
+      </c>
+      <c r="O146" s="2">
+        <v>0</v>
+      </c>
+      <c r="P146" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="2">
+        <v>0</v>
+      </c>
+      <c r="R146" s="2">
+        <v>0</v>
+      </c>
+      <c r="S146" s="2">
+        <v>0</v>
+      </c>
+      <c r="T146" s="2">
+        <v>0</v>
+      </c>
+      <c r="U146" s="2">
+        <v>0</v>
+      </c>
+      <c r="V146" s="2">
+        <v>0</v>
+      </c>
+      <c r="W146" s="2">
+        <v>0</v>
+      </c>
+      <c r="X146" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y146" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB146" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC146" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD146" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE146" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF146" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG146" s="2">
+        <v>2</v>
+      </c>
+      <c r="AH146" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI146" s="1">
         <v>10000</v>
-      </c>
-      <c r="G146" s="2">
-        <v>0</v>
-      </c>
-      <c r="H146" s="2">
-        <v>0</v>
-      </c>
-      <c r="I146" s="2">
-        <v>0</v>
-      </c>
-      <c r="J146" s="2">
-        <v>0</v>
-      </c>
-      <c r="K146" s="2">
-        <v>0</v>
-      </c>
-      <c r="L146" s="2">
-        <v>0</v>
-      </c>
-      <c r="M146" s="2">
-        <v>0</v>
-      </c>
-      <c r="N146" s="2">
-        <v>0</v>
-      </c>
-      <c r="O146" s="2">
-        <v>0</v>
-      </c>
-      <c r="P146" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q146" s="2">
-        <v>0</v>
-      </c>
-      <c r="R146" s="2">
-        <v>0</v>
-      </c>
-      <c r="S146" s="2">
-        <v>0</v>
-      </c>
-      <c r="T146" s="2">
-        <v>0</v>
-      </c>
-      <c r="U146" s="2">
-        <v>0</v>
-      </c>
-      <c r="V146" s="2">
-        <v>0</v>
-      </c>
-      <c r="W146" s="2">
-        <v>0</v>
-      </c>
-      <c r="X146" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y146" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z146" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA146" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB146" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC146" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD146" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE146" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF146" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG146" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH146" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI146" s="2">
-        <v>2</v>
       </c>
       <c r="AJ146" s="1">
         <v>20</v>
@@ -14745,95 +14745,95 @@
       <c r="E147" t="str">
         <v/>
       </c>
-      <c r="F147" s="1">
+      <c r="F147" s="2">
+        <v>0</v>
+      </c>
+      <c r="G147" s="2">
+        <v>0</v>
+      </c>
+      <c r="H147" s="2">
+        <v>0</v>
+      </c>
+      <c r="I147" s="2">
+        <v>0</v>
+      </c>
+      <c r="J147" s="2">
+        <v>0</v>
+      </c>
+      <c r="K147" s="2">
+        <v>0</v>
+      </c>
+      <c r="L147" s="2">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2">
+        <v>0</v>
+      </c>
+      <c r="N147" s="2">
+        <v>0</v>
+      </c>
+      <c r="O147" s="2">
+        <v>0</v>
+      </c>
+      <c r="P147" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="2">
+        <v>0</v>
+      </c>
+      <c r="R147" s="2">
+        <v>0</v>
+      </c>
+      <c r="S147" s="2">
+        <v>0</v>
+      </c>
+      <c r="T147" s="2">
+        <v>0</v>
+      </c>
+      <c r="U147" s="2">
+        <v>0</v>
+      </c>
+      <c r="V147" s="2">
+        <v>0</v>
+      </c>
+      <c r="W147" s="2">
+        <v>0</v>
+      </c>
+      <c r="X147" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z147" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB147" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC147" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD147" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE147" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF147" s="2">
+        <v>2</v>
+      </c>
+      <c r="AG147" s="2">
+        <v>5</v>
+      </c>
+      <c r="AH147" s="2">
+        <v>2</v>
+      </c>
+      <c r="AI147" s="1">
         <v>20000</v>
-      </c>
-      <c r="G147" s="2">
-        <v>0</v>
-      </c>
-      <c r="H147" s="2">
-        <v>0</v>
-      </c>
-      <c r="I147" s="2">
-        <v>0</v>
-      </c>
-      <c r="J147" s="2">
-        <v>0</v>
-      </c>
-      <c r="K147" s="2">
-        <v>0</v>
-      </c>
-      <c r="L147" s="2">
-        <v>0</v>
-      </c>
-      <c r="M147" s="2">
-        <v>0</v>
-      </c>
-      <c r="N147" s="2">
-        <v>0</v>
-      </c>
-      <c r="O147" s="2">
-        <v>0</v>
-      </c>
-      <c r="P147" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q147" s="2">
-        <v>0</v>
-      </c>
-      <c r="R147" s="2">
-        <v>0</v>
-      </c>
-      <c r="S147" s="2">
-        <v>0</v>
-      </c>
-      <c r="T147" s="2">
-        <v>0</v>
-      </c>
-      <c r="U147" s="2">
-        <v>0</v>
-      </c>
-      <c r="V147" s="2">
-        <v>0</v>
-      </c>
-      <c r="W147" s="2">
-        <v>0</v>
-      </c>
-      <c r="X147" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y147" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z147" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA147" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB147" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC147" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD147" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE147" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF147" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG147" s="2">
-        <v>2</v>
-      </c>
-      <c r="AH147" s="2">
-        <v>2</v>
-      </c>
-      <c r="AI147" s="2">
-        <v>5</v>
       </c>
       <c r="AJ147" s="1">
         <v>40</v>
@@ -14858,95 +14858,95 @@
       <c r="E148" s="1">
         <v>9999.99</v>
       </c>
-      <c r="F148" s="1">
+      <c r="F148" s="2">
+        <v>0</v>
+      </c>
+      <c r="G148" s="2">
+        <v>0</v>
+      </c>
+      <c r="H148" s="2">
+        <v>0</v>
+      </c>
+      <c r="I148" s="2">
+        <v>0</v>
+      </c>
+      <c r="J148" s="2">
+        <v>0</v>
+      </c>
+      <c r="K148" s="2">
+        <v>0</v>
+      </c>
+      <c r="L148" s="2">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2">
+        <v>0</v>
+      </c>
+      <c r="N148" s="2">
+        <v>0</v>
+      </c>
+      <c r="O148" s="2">
+        <v>0</v>
+      </c>
+      <c r="P148" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="2">
+        <v>0</v>
+      </c>
+      <c r="R148" s="2">
+        <v>0</v>
+      </c>
+      <c r="S148" s="2">
+        <v>0</v>
+      </c>
+      <c r="T148" s="2">
+        <v>0</v>
+      </c>
+      <c r="U148" s="2">
+        <v>0</v>
+      </c>
+      <c r="V148" s="2">
+        <v>0</v>
+      </c>
+      <c r="W148" s="2">
+        <v>0</v>
+      </c>
+      <c r="X148" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y148" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB148" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC148" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD148" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE148" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF148" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG148" s="2">
+        <v>3</v>
+      </c>
+      <c r="AH148" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI148" s="1">
         <v>9999.99</v>
-      </c>
-      <c r="G148" s="2">
-        <v>0</v>
-      </c>
-      <c r="H148" s="2">
-        <v>0</v>
-      </c>
-      <c r="I148" s="2">
-        <v>0</v>
-      </c>
-      <c r="J148" s="2">
-        <v>0</v>
-      </c>
-      <c r="K148" s="2">
-        <v>0</v>
-      </c>
-      <c r="L148" s="2">
-        <v>0</v>
-      </c>
-      <c r="M148" s="2">
-        <v>0</v>
-      </c>
-      <c r="N148" s="2">
-        <v>0</v>
-      </c>
-      <c r="O148" s="2">
-        <v>0</v>
-      </c>
-      <c r="P148" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q148" s="2">
-        <v>0</v>
-      </c>
-      <c r="R148" s="2">
-        <v>0</v>
-      </c>
-      <c r="S148" s="2">
-        <v>0</v>
-      </c>
-      <c r="T148" s="2">
-        <v>0</v>
-      </c>
-      <c r="U148" s="2">
-        <v>0</v>
-      </c>
-      <c r="V148" s="2">
-        <v>0</v>
-      </c>
-      <c r="W148" s="2">
-        <v>0</v>
-      </c>
-      <c r="X148" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y148" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z148" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA148" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB148" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC148" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD148" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE148" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF148" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG148" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH148" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI148" s="2">
-        <v>3</v>
       </c>
       <c r="AJ148" s="1">
         <v>20</v>
@@ -14971,95 +14971,95 @@
       <c r="E149" s="1">
         <v>99999.99</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F149" s="2">
+        <v>0</v>
+      </c>
+      <c r="G149" s="2">
+        <v>0</v>
+      </c>
+      <c r="H149" s="2">
+        <v>0</v>
+      </c>
+      <c r="I149" s="2">
+        <v>0</v>
+      </c>
+      <c r="J149" s="2">
+        <v>0</v>
+      </c>
+      <c r="K149" s="2">
+        <v>0</v>
+      </c>
+      <c r="L149" s="2">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2">
+        <v>0</v>
+      </c>
+      <c r="N149" s="2">
+        <v>0</v>
+      </c>
+      <c r="O149" s="2">
+        <v>0</v>
+      </c>
+      <c r="P149" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="2">
+        <v>0</v>
+      </c>
+      <c r="R149" s="2">
+        <v>0</v>
+      </c>
+      <c r="S149" s="2">
+        <v>0</v>
+      </c>
+      <c r="T149" s="2">
+        <v>0</v>
+      </c>
+      <c r="U149" s="2">
+        <v>0</v>
+      </c>
+      <c r="V149" s="2">
+        <v>0</v>
+      </c>
+      <c r="W149" s="2">
+        <v>0</v>
+      </c>
+      <c r="X149" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y149" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z149" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB149" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC149" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD149" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE149" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF149" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG149" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH149" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI149" s="1">
         <v>99999.99</v>
-      </c>
-      <c r="G149" s="2">
-        <v>0</v>
-      </c>
-      <c r="H149" s="2">
-        <v>0</v>
-      </c>
-      <c r="I149" s="2">
-        <v>0</v>
-      </c>
-      <c r="J149" s="2">
-        <v>0</v>
-      </c>
-      <c r="K149" s="2">
-        <v>0</v>
-      </c>
-      <c r="L149" s="2">
-        <v>0</v>
-      </c>
-      <c r="M149" s="2">
-        <v>0</v>
-      </c>
-      <c r="N149" s="2">
-        <v>0</v>
-      </c>
-      <c r="O149" s="2">
-        <v>0</v>
-      </c>
-      <c r="P149" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q149" s="2">
-        <v>0</v>
-      </c>
-      <c r="R149" s="2">
-        <v>0</v>
-      </c>
-      <c r="S149" s="2">
-        <v>0</v>
-      </c>
-      <c r="T149" s="2">
-        <v>0</v>
-      </c>
-      <c r="U149" s="2">
-        <v>0</v>
-      </c>
-      <c r="V149" s="2">
-        <v>0</v>
-      </c>
-      <c r="W149" s="2">
-        <v>0</v>
-      </c>
-      <c r="X149" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y149" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z149" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA149" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB149" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC149" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD149" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE149" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF149" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG149" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH149" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI149" s="2">
-        <v>1</v>
       </c>
       <c r="AJ149" s="1">
         <v>20</v>
@@ -15084,95 +15084,95 @@
       <c r="E150" s="1">
         <v>999999.99</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F150" s="2">
+        <v>0</v>
+      </c>
+      <c r="G150" s="2">
+        <v>0</v>
+      </c>
+      <c r="H150" s="2">
+        <v>0</v>
+      </c>
+      <c r="I150" s="2">
+        <v>0</v>
+      </c>
+      <c r="J150" s="2">
+        <v>0</v>
+      </c>
+      <c r="K150" s="2">
+        <v>0</v>
+      </c>
+      <c r="L150" s="2">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2">
+        <v>0</v>
+      </c>
+      <c r="N150" s="2">
+        <v>0</v>
+      </c>
+      <c r="O150" s="2">
+        <v>0</v>
+      </c>
+      <c r="P150" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="2">
+        <v>0</v>
+      </c>
+      <c r="R150" s="2">
+        <v>0</v>
+      </c>
+      <c r="S150" s="2">
+        <v>0</v>
+      </c>
+      <c r="T150" s="2">
+        <v>0</v>
+      </c>
+      <c r="U150" s="2">
+        <v>0</v>
+      </c>
+      <c r="V150" s="2">
+        <v>0</v>
+      </c>
+      <c r="W150" s="2">
+        <v>0</v>
+      </c>
+      <c r="X150" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y150" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB150" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD150" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE150" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF150" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG150" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH150" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI150" s="1">
         <v>999999.99</v>
-      </c>
-      <c r="G150" s="2">
-        <v>0</v>
-      </c>
-      <c r="H150" s="2">
-        <v>0</v>
-      </c>
-      <c r="I150" s="2">
-        <v>0</v>
-      </c>
-      <c r="J150" s="2">
-        <v>0</v>
-      </c>
-      <c r="K150" s="2">
-        <v>0</v>
-      </c>
-      <c r="L150" s="2">
-        <v>0</v>
-      </c>
-      <c r="M150" s="2">
-        <v>0</v>
-      </c>
-      <c r="N150" s="2">
-        <v>0</v>
-      </c>
-      <c r="O150" s="2">
-        <v>0</v>
-      </c>
-      <c r="P150" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q150" s="2">
-        <v>0</v>
-      </c>
-      <c r="R150" s="2">
-        <v>0</v>
-      </c>
-      <c r="S150" s="2">
-        <v>0</v>
-      </c>
-      <c r="T150" s="2">
-        <v>0</v>
-      </c>
-      <c r="U150" s="2">
-        <v>0</v>
-      </c>
-      <c r="V150" s="2">
-        <v>0</v>
-      </c>
-      <c r="W150" s="2">
-        <v>0</v>
-      </c>
-      <c r="X150" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y150" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z150" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA150" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB150" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC150" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD150" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE150" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF150" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG150" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH150" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI150" s="2">
-        <v>1</v>
       </c>
       <c r="AJ150" s="1">
         <v>20</v>
@@ -15197,8 +15197,8 @@
       <c r="E151" s="1">
         <v>2</v>
       </c>
-      <c r="F151" s="1">
-        <v>54</v>
+      <c r="F151" s="2">
+        <v>1</v>
       </c>
       <c r="G151" s="2">
         <v>1</v>
@@ -15279,13 +15279,13 @@
         <v>1</v>
       </c>
       <c r="AG151" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AH151" s="2">
         <v>27</v>
       </c>
-      <c r="AI151" s="2">
-        <v>7</v>
+      <c r="AI151" s="1">
+        <v>54</v>
       </c>
       <c r="AJ151" s="1">
         <v>540</v>
@@ -15310,8 +15310,8 @@
       <c r="E152" s="1">
         <v>5</v>
       </c>
-      <c r="F152" s="1">
-        <v>-10</v>
+      <c r="F152" s="2">
+        <v>0</v>
       </c>
       <c r="G152" s="2">
         <v>0</v>
@@ -15386,19 +15386,19 @@
         <v>0</v>
       </c>
       <c r="AE152" s="2">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AF152" s="2">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="AG152" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH152" s="2">
         <v>-2</v>
       </c>
-      <c r="AI152" s="2">
-        <v>4</v>
+      <c r="AI152" s="1">
+        <v>-10</v>
       </c>
       <c r="AJ152" s="1">
         <v>-40</v>
@@ -15423,95 +15423,95 @@
       <c r="E153" t="str">
         <v/>
       </c>
-      <c r="F153" t="str">
+      <c r="F153" s="2">
+        <v>0</v>
+      </c>
+      <c r="G153" s="2">
+        <v>0</v>
+      </c>
+      <c r="H153" s="2">
+        <v>0</v>
+      </c>
+      <c r="I153" s="2">
+        <v>0</v>
+      </c>
+      <c r="J153" s="2">
+        <v>0</v>
+      </c>
+      <c r="K153" s="2">
+        <v>0</v>
+      </c>
+      <c r="L153" s="2">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2">
+        <v>0</v>
+      </c>
+      <c r="N153" s="2">
+        <v>0</v>
+      </c>
+      <c r="O153" s="2">
+        <v>0</v>
+      </c>
+      <c r="P153" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="2">
+        <v>0</v>
+      </c>
+      <c r="R153" s="2">
+        <v>0</v>
+      </c>
+      <c r="S153" s="2">
+        <v>0</v>
+      </c>
+      <c r="T153" s="2">
+        <v>0</v>
+      </c>
+      <c r="U153" s="2">
+        <v>0</v>
+      </c>
+      <c r="V153" s="2">
+        <v>0</v>
+      </c>
+      <c r="W153" s="2">
+        <v>0</v>
+      </c>
+      <c r="X153" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y153" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z153" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA153" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB153" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC153" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD153" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE153" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF153" s="2">
+        <v>4</v>
+      </c>
+      <c r="AG153" s="2">
+        <v>4</v>
+      </c>
+      <c r="AH153" s="2">
+        <v>4</v>
+      </c>
+      <c r="AI153" t="str">
         <v/>
-      </c>
-      <c r="G153" s="2">
-        <v>0</v>
-      </c>
-      <c r="H153" s="2">
-        <v>0</v>
-      </c>
-      <c r="I153" s="2">
-        <v>0</v>
-      </c>
-      <c r="J153" s="2">
-        <v>0</v>
-      </c>
-      <c r="K153" s="2">
-        <v>0</v>
-      </c>
-      <c r="L153" s="2">
-        <v>0</v>
-      </c>
-      <c r="M153" s="2">
-        <v>0</v>
-      </c>
-      <c r="N153" s="2">
-        <v>0</v>
-      </c>
-      <c r="O153" s="2">
-        <v>0</v>
-      </c>
-      <c r="P153" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q153" s="2">
-        <v>0</v>
-      </c>
-      <c r="R153" s="2">
-        <v>0</v>
-      </c>
-      <c r="S153" s="2">
-        <v>0</v>
-      </c>
-      <c r="T153" s="2">
-        <v>0</v>
-      </c>
-      <c r="U153" s="2">
-        <v>0</v>
-      </c>
-      <c r="V153" s="2">
-        <v>0</v>
-      </c>
-      <c r="W153" s="2">
-        <v>0</v>
-      </c>
-      <c r="X153" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y153" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z153" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA153" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB153" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC153" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD153" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE153" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF153" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG153" s="2">
-        <v>4</v>
-      </c>
-      <c r="AH153" s="2">
-        <v>4</v>
-      </c>
-      <c r="AI153" s="2">
-        <v>4</v>
       </c>
       <c r="AJ153" s="1">
         <v>80</v>
@@ -15536,8 +15536,8 @@
       <c r="E154" s="1">
         <v>3</v>
       </c>
-      <c r="F154" s="1">
-        <v>6</v>
+      <c r="F154" s="2">
+        <v>0</v>
       </c>
       <c r="G154" s="2">
         <v>0</v>
@@ -15615,16 +15615,16 @@
         <v>0</v>
       </c>
       <c r="AF154" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG154" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH154" s="2">
         <v>2</v>
       </c>
-      <c r="AI154" s="2">
-        <v>4</v>
+      <c r="AI154" s="1">
+        <v>6</v>
       </c>
       <c r="AJ154" s="1">
         <v>40</v>
@@ -15649,7 +15649,7 @@
       <c r="E155" s="1">
         <v>4</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="2">
         <v>0</v>
       </c>
       <c r="G155" s="2">
@@ -15731,13 +15731,13 @@
         <v>0</v>
       </c>
       <c r="AG155" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH155" s="2">
         <v>0</v>
       </c>
-      <c r="AI155" s="2">
-        <v>5</v>
+      <c r="AI155" s="1">
+        <v>0</v>
       </c>
       <c r="AJ155" s="1">
         <v>0</v>
@@ -15762,95 +15762,95 @@
       <c r="E156" s="1">
         <v>4</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F156" s="2">
+        <v>0</v>
+      </c>
+      <c r="G156" s="2">
+        <v>0</v>
+      </c>
+      <c r="H156" s="2">
+        <v>0</v>
+      </c>
+      <c r="I156" s="2">
+        <v>0</v>
+      </c>
+      <c r="J156" s="2">
+        <v>0</v>
+      </c>
+      <c r="K156" s="2">
+        <v>0</v>
+      </c>
+      <c r="L156" s="2">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2">
+        <v>0</v>
+      </c>
+      <c r="N156" s="2">
+        <v>0</v>
+      </c>
+      <c r="O156" s="2">
+        <v>0</v>
+      </c>
+      <c r="P156" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q156" s="2">
+        <v>0</v>
+      </c>
+      <c r="R156" s="2">
+        <v>0</v>
+      </c>
+      <c r="S156" s="2">
+        <v>0</v>
+      </c>
+      <c r="T156" s="2">
+        <v>0</v>
+      </c>
+      <c r="U156" s="2">
+        <v>0</v>
+      </c>
+      <c r="V156" s="2">
+        <v>0</v>
+      </c>
+      <c r="W156" s="2">
+        <v>0</v>
+      </c>
+      <c r="X156" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y156" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z156" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA156" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB156" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC156" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD156" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE156" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF156" s="2">
+        <v>3</v>
+      </c>
+      <c r="AG156" s="2">
+        <v>-3</v>
+      </c>
+      <c r="AH156" s="2">
+        <v>3</v>
+      </c>
+      <c r="AI156" s="1">
         <v>12</v>
-      </c>
-      <c r="G156" s="2">
-        <v>0</v>
-      </c>
-      <c r="H156" s="2">
-        <v>0</v>
-      </c>
-      <c r="I156" s="2">
-        <v>0</v>
-      </c>
-      <c r="J156" s="2">
-        <v>0</v>
-      </c>
-      <c r="K156" s="2">
-        <v>0</v>
-      </c>
-      <c r="L156" s="2">
-        <v>0</v>
-      </c>
-      <c r="M156" s="2">
-        <v>0</v>
-      </c>
-      <c r="N156" s="2">
-        <v>0</v>
-      </c>
-      <c r="O156" s="2">
-        <v>0</v>
-      </c>
-      <c r="P156" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q156" s="2">
-        <v>0</v>
-      </c>
-      <c r="R156" s="2">
-        <v>0</v>
-      </c>
-      <c r="S156" s="2">
-        <v>0</v>
-      </c>
-      <c r="T156" s="2">
-        <v>0</v>
-      </c>
-      <c r="U156" s="2">
-        <v>0</v>
-      </c>
-      <c r="V156" s="2">
-        <v>0</v>
-      </c>
-      <c r="W156" s="2">
-        <v>0</v>
-      </c>
-      <c r="X156" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y156" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z156" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA156" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB156" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC156" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD156" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE156" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF156" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG156" s="2">
-        <v>3</v>
-      </c>
-      <c r="AH156" s="2">
-        <v>3</v>
-      </c>
-      <c r="AI156" s="2">
-        <v>-3</v>
       </c>
       <c r="AJ156" s="1">
         <v>60</v>
@@ -15875,95 +15875,95 @@
       <c r="E157" s="1">
         <v>4</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="2">
+        <v>0</v>
+      </c>
+      <c r="G157" s="2">
+        <v>0</v>
+      </c>
+      <c r="H157" s="2">
+        <v>0</v>
+      </c>
+      <c r="I157" s="2">
+        <v>0</v>
+      </c>
+      <c r="J157" s="2">
+        <v>0</v>
+      </c>
+      <c r="K157" s="2">
+        <v>0</v>
+      </c>
+      <c r="L157" s="2">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2">
+        <v>0</v>
+      </c>
+      <c r="N157" s="2">
+        <v>0</v>
+      </c>
+      <c r="O157" s="2">
+        <v>0</v>
+      </c>
+      <c r="P157" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q157" s="2">
+        <v>0</v>
+      </c>
+      <c r="R157" s="2">
+        <v>0</v>
+      </c>
+      <c r="S157" s="2">
+        <v>0</v>
+      </c>
+      <c r="T157" s="2">
+        <v>0</v>
+      </c>
+      <c r="U157" s="2">
+        <v>0</v>
+      </c>
+      <c r="V157" s="2">
+        <v>0</v>
+      </c>
+      <c r="W157" s="2">
+        <v>0</v>
+      </c>
+      <c r="X157" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="2">
+        <v>3</v>
+      </c>
+      <c r="AG157" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="2">
+        <v>3</v>
+      </c>
+      <c r="AI157" s="1">
         <v>12</v>
-      </c>
-      <c r="G157" s="2">
-        <v>0</v>
-      </c>
-      <c r="H157" s="2">
-        <v>0</v>
-      </c>
-      <c r="I157" s="2">
-        <v>0</v>
-      </c>
-      <c r="J157" s="2">
-        <v>0</v>
-      </c>
-      <c r="K157" s="2">
-        <v>0</v>
-      </c>
-      <c r="L157" s="2">
-        <v>0</v>
-      </c>
-      <c r="M157" s="2">
-        <v>0</v>
-      </c>
-      <c r="N157" s="2">
-        <v>0</v>
-      </c>
-      <c r="O157" s="2">
-        <v>0</v>
-      </c>
-      <c r="P157" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q157" s="2">
-        <v>0</v>
-      </c>
-      <c r="R157" s="2">
-        <v>0</v>
-      </c>
-      <c r="S157" s="2">
-        <v>0</v>
-      </c>
-      <c r="T157" s="2">
-        <v>0</v>
-      </c>
-      <c r="U157" s="2">
-        <v>0</v>
-      </c>
-      <c r="V157" s="2">
-        <v>0</v>
-      </c>
-      <c r="W157" s="2">
-        <v>0</v>
-      </c>
-      <c r="X157" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y157" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z157" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA157" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB157" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC157" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD157" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE157" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF157" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG157" s="2">
-        <v>3</v>
-      </c>
-      <c r="AH157" s="2">
-        <v>3</v>
-      </c>
-      <c r="AI157" s="2">
-        <v>0</v>
       </c>
       <c r="AJ157" s="1">
         <v>60</v>
@@ -15976,8 +15976,8 @@
       <c r="A158" t="str">
         <v>TOTAL GERAL</v>
       </c>
-      <c r="F158" s="1">
-        <v>1156001.97</v>
+      <c r="F158" s="2">
+        <v>181</v>
       </c>
       <c r="G158" s="2">
         <v>181</v>
@@ -16052,16 +16052,16 @@
         <v>181</v>
       </c>
       <c r="AE158" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AF158" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG158" s="2">
         <v>203</v>
       </c>
       <c r="AH158" s="2">
         <v>4906</v>
+      </c>
+      <c r="AI158" s="1">
+        <v>1156001.97</v>
       </c>
       <c r="AJ158" s="1">
         <v>98120</v>

--- a/docs/validacao-visual/2026-10-vendas-mapa/vendas-27-meses.xlsx
+++ b/docs/validacao-visual/2026-10-vendas-mapa/vendas-27-meses.xlsx
@@ -456,7 +456,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gerado em: 16/10/2026, 11:17</v>
+        <v>Gerado em: 16/10/2026, 12:40</v>
       </c>
     </row>
     <row r="5">

--- a/docs/validacao-visual/2026-10-vendas-mapa/vendas-27-meses.xlsx
+++ b/docs/validacao-visual/2026-10-vendas-mapa/vendas-27-meses.xlsx
@@ -456,7 +456,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gerado em: 26/10/2026, 11:15</v>
+        <v>Gerado em: 26/10/2026, 11:43</v>
       </c>
     </row>
     <row r="5">
